--- a/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
+++ b/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186E1916-3B38-4C04-B84E-3EE2BA180651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A769C7-5DDA-4443-B9A4-54B4D6ADD9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
     <sheet name="Regions" sheetId="15" r:id="rId2"/>
     <sheet name="PWR" sheetId="19" r:id="rId3"/>
     <sheet name="SYS" sheetId="28" r:id="rId4"/>
-    <sheet name="SUP" sheetId="11" r:id="rId5"/>
-    <sheet name="SRV" sheetId="26" r:id="rId6"/>
-    <sheet name="TRA" sheetId="27" r:id="rId7"/>
+    <sheet name="RSD" sheetId="30" r:id="rId5"/>
+    <sheet name="SUP" sheetId="11" r:id="rId6"/>
+    <sheet name="SRV" sheetId="26" r:id="rId7"/>
+    <sheet name="TRA" sheetId="27" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="__123Graph_AEUMILKPN" localSheetId="0" hidden="1">#REF!</definedName>
@@ -195,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="266">
   <si>
     <t>UC_N</t>
   </si>
@@ -718,9 +719,6 @@
     <t>Source: CLIMATE ACTION PLAN 2023, CAP23</t>
   </si>
   <si>
-    <t>Minimum solar PV capacity</t>
-  </si>
-  <si>
     <t>Max Wind Offshore Capacity</t>
   </si>
   <si>
@@ -967,9 +965,6 @@
     <t>https://cms.eirgrid.ie/sites/default/files/publications/19035-EirGrid-Generation-Capacity-Statement-Combined-2023-V5-Jan-2024.pdf</t>
   </si>
   <si>
-    <t>FX</t>
-  </si>
-  <si>
     <t>UC_Min_PV_Cap</t>
   </si>
   <si>
@@ -992,13 +987,40 @@
   </si>
   <si>
     <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>*UC_Max_PV_Cap</t>
+  </si>
+  <si>
+    <t>*P*SOL-PV*</t>
+  </si>
+  <si>
+    <t>UC_T</t>
+  </si>
+  <si>
+    <t>UC_RSD_GAS_OIL_ratio</t>
+  </si>
+  <si>
+    <t>FT-RSDKER</t>
+  </si>
+  <si>
+    <t>RSDKER</t>
+  </si>
+  <si>
+    <t>The share ratio for natural gas and kerosene in residential sector</t>
+  </si>
+  <si>
+    <t>FT-RSDGAS</t>
+  </si>
+  <si>
+    <t>RSDGAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="30">
+  <numFmts count="32">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
@@ -1029,6 +1051,8 @@
     <numFmt numFmtId="189" formatCode="[$-340A]d&quot; de &quot;mmmm&quot; de &quot;yyyy;@"/>
     <numFmt numFmtId="190" formatCode="0.0%"/>
     <numFmt numFmtId="191" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="193" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="195" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="137">
     <font>
@@ -2848,7 +2872,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4137">
+  <cellStyleXfs count="4437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -7148,8 +7172,308 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="121" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7334,8 +7658,22 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4137">
+  <cellStyles count="4437">
     <cellStyle name="0,0_x000a__x000a_NA_x000a__x000a_" xfId="112" xr:uid="{6012D418-BB45-4405-A049-43BDF7D6C774}"/>
     <cellStyle name="1o.nível" xfId="113" xr:uid="{0734992E-F9C5-4098-8F4D-D7496B3C00AE}"/>
     <cellStyle name="20% - Accent1" xfId="87" builtinId="30" customBuiltin="1"/>
@@ -8145,35 +8483,67 @@
     <cellStyle name="Comma 2" xfId="9" xr:uid="{775BEC45-7458-497B-BB11-55064E667555}"/>
     <cellStyle name="Comma 2 2" xfId="10" xr:uid="{F65F9B0F-DF7C-4E9E-AFBF-86D7F3675750}"/>
     <cellStyle name="Comma 2 2 2" xfId="13" xr:uid="{FC34B759-F64A-45B3-8D66-7A9670F594A3}"/>
+    <cellStyle name="Comma 2 2 2 2" xfId="4141" xr:uid="{07852662-8325-4B8D-804B-8A451D1FEBF1}"/>
     <cellStyle name="Comma 2 2 3" xfId="23" xr:uid="{33EBBC6C-C597-4B1D-AC39-F47C490B8822}"/>
+    <cellStyle name="Comma 2 2 3 2" xfId="4144" xr:uid="{48C704DB-457E-44D7-B806-E5FF5BACD00B}"/>
     <cellStyle name="Comma 2 2 4" xfId="68" xr:uid="{43C51634-3BB2-423E-A0F8-35BC9068AE84}"/>
+    <cellStyle name="Comma 2 2 4 2" xfId="4150" xr:uid="{ED3BDBE6-6B24-4B8F-805A-953CD36C279E}"/>
+    <cellStyle name="Comma 2 2 5" xfId="4138" xr:uid="{A8A824A1-13A8-45D9-944C-4E527E2AC8C0}"/>
     <cellStyle name="Comma 2 3" xfId="12" xr:uid="{4A17FA2D-8470-4CF6-8DC2-474CAE021A78}"/>
     <cellStyle name="Comma 2 3 2" xfId="24" xr:uid="{68F5AAB6-9DA7-40D2-8AEF-747446C06B60}"/>
+    <cellStyle name="Comma 2 3 2 2" xfId="4145" xr:uid="{0F22F3C0-6CE0-4791-94C5-876E6E170D64}"/>
     <cellStyle name="Comma 2 3 3" xfId="69" xr:uid="{6C5D0EAF-6DBB-4C14-B44E-E0FF7F58D108}"/>
+    <cellStyle name="Comma 2 3 3 2" xfId="4151" xr:uid="{15FEDCAB-09F6-4B05-8BFF-BDC2FC6692EE}"/>
     <cellStyle name="Comma 2 3 4" xfId="866" xr:uid="{8D883AEA-5560-4D08-ABB6-935D9070FD48}"/>
+    <cellStyle name="Comma 2 3 4 2" xfId="4155" xr:uid="{B9B135D0-256F-4DC5-A349-5BFA4141CE8E}"/>
+    <cellStyle name="Comma 2 3 5" xfId="4140" xr:uid="{58AE4F18-C92F-490B-8FAF-C74D3AF519A2}"/>
     <cellStyle name="Comma 2 4" xfId="20" xr:uid="{5AD248CC-0E02-4314-9EA5-5EF75B2CABF3}"/>
     <cellStyle name="Comma 2 4 2" xfId="868" xr:uid="{94FA72A4-15C2-41F8-ABD3-C0BA115477DC}"/>
+    <cellStyle name="Comma 2 4 2 2" xfId="4157" xr:uid="{89F0AEFB-F6FD-4055-B00E-071A7F609582}"/>
     <cellStyle name="Comma 2 4 3" xfId="867" xr:uid="{BE9D831D-B007-4816-8D36-BD9AC9240194}"/>
+    <cellStyle name="Comma 2 4 3 2" xfId="4156" xr:uid="{8550A731-5DB2-44B2-BF42-D6317ECC4DA3}"/>
+    <cellStyle name="Comma 2 4 4" xfId="4143" xr:uid="{2A95131E-A76D-4C98-9DE8-EE2DECCE1D98}"/>
     <cellStyle name="Comma 2 5" xfId="67" xr:uid="{A5CCE614-5023-4389-B37A-DC20AB2349F9}"/>
     <cellStyle name="Comma 2 5 2" xfId="870" xr:uid="{2E63107A-582C-435E-8027-B797C434B90A}"/>
+    <cellStyle name="Comma 2 5 2 2" xfId="4159" xr:uid="{5AC44BC9-BBA5-41A8-BAAD-453B19F72BCA}"/>
     <cellStyle name="Comma 2 5 3" xfId="871" xr:uid="{EF55991B-F02A-4265-8DCD-01E0774CCB8A}"/>
+    <cellStyle name="Comma 2 5 3 2" xfId="4160" xr:uid="{3B74A9B0-2095-417A-9BB1-1CE5BAE66385}"/>
     <cellStyle name="Comma 2 5 4" xfId="869" xr:uid="{21A4DEB6-B012-44F3-A3EC-D2CE3C65426A}"/>
+    <cellStyle name="Comma 2 5 4 2" xfId="4158" xr:uid="{D9B9A526-2E79-48A8-90AD-9997A9A1BFD6}"/>
+    <cellStyle name="Comma 2 5 5" xfId="4149" xr:uid="{EA9E3C66-81C7-47B6-8667-2E0AE59C010D}"/>
     <cellStyle name="Comma 2 6" xfId="872" xr:uid="{58F0B02D-38B9-4B41-A4CB-7CC2073B239C}"/>
     <cellStyle name="Comma 2 6 2" xfId="873" xr:uid="{D3E5C4D3-CCFB-4225-99D0-A0A4A87E70A2}"/>
+    <cellStyle name="Comma 2 6 2 2" xfId="4162" xr:uid="{CBDC5089-A829-42E8-AF34-3C0ECC933A73}"/>
     <cellStyle name="Comma 2 6 3" xfId="874" xr:uid="{F3CB42E4-D747-4CA7-9744-0FAB3FC94FDC}"/>
+    <cellStyle name="Comma 2 6 3 2" xfId="4163" xr:uid="{C0F3BD0C-BD62-4074-9288-36159995BDFF}"/>
+    <cellStyle name="Comma 2 6 4" xfId="4161" xr:uid="{68A19C6B-637A-454A-8BA5-3802C212183C}"/>
     <cellStyle name="Comma 2 7" xfId="875" xr:uid="{1E5834F5-BD35-49FB-9F61-2C4FD54A1E1D}"/>
+    <cellStyle name="Comma 2 7 2" xfId="4164" xr:uid="{92B92A04-D11E-474C-9216-95BAF3AFB312}"/>
     <cellStyle name="Comma 2 8" xfId="865" xr:uid="{C61E92F0-77D2-42CB-96D4-A4D33EFFA3AA}"/>
+    <cellStyle name="Comma 2 8 2" xfId="4154" xr:uid="{06FE1B21-3AAB-4FE9-A203-C231D2DBEAD7}"/>
+    <cellStyle name="Comma 2 9" xfId="4137" xr:uid="{E2337F27-84F7-45F5-8011-668A3D101DF3}"/>
     <cellStyle name="Comma 3" xfId="11" xr:uid="{03D7843A-4C0D-4CBE-89E7-EB9FDF20B2F4}"/>
     <cellStyle name="Comma 3 2" xfId="25" xr:uid="{FFBEAD64-207A-4D48-9026-515F6A5A380D}"/>
+    <cellStyle name="Comma 3 2 2" xfId="4146" xr:uid="{CAABB325-80A1-4F4A-AD89-7D447663282B}"/>
     <cellStyle name="Comma 3 3" xfId="70" xr:uid="{C89024A7-B373-43C3-A92C-8FE7821B8E42}"/>
+    <cellStyle name="Comma 3 3 2" xfId="4152" xr:uid="{C3CA0597-A061-4ED4-A787-D5F50DE0F9C9}"/>
     <cellStyle name="Comma 3 4" xfId="876" xr:uid="{7D14FBE4-A72D-4F4C-BED9-FD3AF6BEE893}"/>
+    <cellStyle name="Comma 3 4 2" xfId="4165" xr:uid="{0C505781-9CEE-491D-BA2F-EE3FF72DFD51}"/>
+    <cellStyle name="Comma 3 5" xfId="4139" xr:uid="{193CB22A-9018-4CF4-A033-E6DC76C25093}"/>
     <cellStyle name="Comma 4" xfId="65" xr:uid="{63A39079-42A5-49E0-8D94-FDEFE01A816F}"/>
     <cellStyle name="Comma 4 2" xfId="71" xr:uid="{0398E1B0-6A4A-4FF9-AB5E-8532DF02A1EC}"/>
+    <cellStyle name="Comma 4 2 2" xfId="4153" xr:uid="{BAB11E65-34AE-4818-897A-4D84C19E7B55}"/>
     <cellStyle name="Comma 4 3" xfId="877" xr:uid="{27E9EB3B-FB7F-452F-AB0E-CDB048E5C673}"/>
+    <cellStyle name="Comma 4 3 2" xfId="4166" xr:uid="{AA2C2852-FE98-484A-B7E8-78B157C757A4}"/>
+    <cellStyle name="Comma 4 4" xfId="4147" xr:uid="{FD699533-D216-4CDD-AFC1-34756834C036}"/>
     <cellStyle name="Comma 5" xfId="15" xr:uid="{A0D20F9D-D9AB-473B-B062-F47231DDC441}"/>
     <cellStyle name="Comma 5 2" xfId="66" xr:uid="{BD76CA48-FB84-4319-9656-8CAA840BFFD3}"/>
+    <cellStyle name="Comma 5 2 2" xfId="4148" xr:uid="{E4A90FDE-BF6A-4FBF-8AD9-66D3DCE9BC9B}"/>
     <cellStyle name="Comma 5 3" xfId="878" xr:uid="{611FF933-56D9-4ECE-8F5D-9E2596AE969B}"/>
+    <cellStyle name="Comma 5 3 2" xfId="4167" xr:uid="{48F45E15-F114-4153-BF45-CEF3A01C9212}"/>
+    <cellStyle name="Comma 5 4" xfId="4142" xr:uid="{8B5C0702-6B6A-42BF-BE31-C10A1AB1C064}"/>
     <cellStyle name="Comma 6" xfId="879" xr:uid="{76A3408F-4733-4A2E-97C3-F862809BA751}"/>
+    <cellStyle name="Comma 6 2" xfId="4168" xr:uid="{6A879557-7755-4E25-89EF-00D3F0274696}"/>
     <cellStyle name="Comma 7" xfId="864" xr:uid="{A24B4F39-2AAE-4882-9604-1882DAE2AE82}"/>
     <cellStyle name="Comma0" xfId="880" xr:uid="{429B1CEE-FBE2-4D13-B65D-FDF726686843}"/>
     <cellStyle name="Currency 2" xfId="881" xr:uid="{84B2FD7A-FF46-400D-86E5-4530C8D91EC7}"/>
@@ -8629,41 +8999,75 @@
     <cellStyle name="Linked Cell 2 2" xfId="1314" xr:uid="{5311C406-73A9-480D-8072-07610E8D4DF1}"/>
     <cellStyle name="Millares [0] 2" xfId="1315" xr:uid="{A8AC05A4-2501-4B45-9D89-B1293C8B1759}"/>
     <cellStyle name="Millares [0] 2 10" xfId="1316" xr:uid="{3EE08C91-381C-4A01-B8DA-B7527A42C8BC}"/>
+    <cellStyle name="Millares [0] 2 10 2" xfId="4169" xr:uid="{958D0231-0DA5-4511-AAFF-D970535F81D1}"/>
     <cellStyle name="Millares [0] 2 2" xfId="1317" xr:uid="{B6F3CD74-2197-4BC7-8C29-36DD66C3270D}"/>
     <cellStyle name="Millares [0] 2 2 2" xfId="1318" xr:uid="{FD4CDCB6-BDBE-42C1-947E-9A4D08005E7B}"/>
     <cellStyle name="Millares [0] 2 2 2 2" xfId="1319" xr:uid="{0F4A016D-6045-4630-B73B-5A0C451F6B68}"/>
+    <cellStyle name="Millares [0] 2 2 2 2 2" xfId="4171" xr:uid="{1D1F1D34-1149-498A-BC9B-0D3D41105A47}"/>
     <cellStyle name="Millares [0] 2 2 2 3" xfId="1320" xr:uid="{4FA788DE-34A7-409C-9C0E-51087A777D35}"/>
     <cellStyle name="Millares [0] 2 2 2 3 2" xfId="1321" xr:uid="{999E280B-1E14-4186-994E-8AA2F4351D1A}"/>
+    <cellStyle name="Millares [0] 2 2 2 3 2 2" xfId="4173" xr:uid="{526A7CBC-0154-4477-B85B-2BC9180A3FC0}"/>
+    <cellStyle name="Millares [0] 2 2 2 3 3" xfId="4172" xr:uid="{D23F4185-A07B-41ED-A19E-784CBB67BAAB}"/>
     <cellStyle name="Millares [0] 2 2 2 4" xfId="1322" xr:uid="{873ED4D7-44DA-461C-8F71-E002DD047875}"/>
     <cellStyle name="Millares [0] 2 2 2 4 2" xfId="1323" xr:uid="{82F27EF5-9E14-4C80-90E6-D8EB91763A29}"/>
+    <cellStyle name="Millares [0] 2 2 2 4 2 2" xfId="4175" xr:uid="{29ADC13F-24AD-4655-918C-6930AFE83561}"/>
     <cellStyle name="Millares [0] 2 2 2 4 3" xfId="1324" xr:uid="{E8D19282-9529-4609-A514-03B2E5257D3A}"/>
+    <cellStyle name="Millares [0] 2 2 2 4 3 2" xfId="4176" xr:uid="{0A0C81FF-2FCA-43AB-80AB-F2E2EA9D0427}"/>
+    <cellStyle name="Millares [0] 2 2 2 4 4" xfId="4174" xr:uid="{0DD2174B-5C80-4973-8538-EEEDF5F5F0D9}"/>
     <cellStyle name="Millares [0] 2 2 2 5" xfId="1325" xr:uid="{35DAF892-4743-4DF7-B3D2-427E4165E83B}"/>
     <cellStyle name="Millares [0] 2 2 2 5 2" xfId="1326" xr:uid="{AC66CAC4-5874-4DD5-8F1D-D86B3C13BFD2}"/>
+    <cellStyle name="Millares [0] 2 2 2 5 2 2" xfId="4178" xr:uid="{6D340FD0-448A-48F3-ACEC-B6ECA388B1D7}"/>
     <cellStyle name="Millares [0] 2 2 2 5 3" xfId="1327" xr:uid="{12379C4F-8E97-41AC-BE1F-8DE143E1FEE0}"/>
+    <cellStyle name="Millares [0] 2 2 2 5 3 2" xfId="4179" xr:uid="{9C030EF3-25B3-4434-BF3F-AB0BAC2B37DE}"/>
+    <cellStyle name="Millares [0] 2 2 2 5 4" xfId="4177" xr:uid="{8FEE46D3-1A3A-47B2-9110-AD7A11E5D6E7}"/>
     <cellStyle name="Millares [0] 2 2 2 6" xfId="1328" xr:uid="{E380992A-7721-4819-8D77-611F6C1F6C57}"/>
+    <cellStyle name="Millares [0] 2 2 2 6 2" xfId="4180" xr:uid="{C3FB6D8E-DEDC-41A0-ADA0-1ECFA6D765BF}"/>
+    <cellStyle name="Millares [0] 2 2 2 7" xfId="4170" xr:uid="{4A7E6447-69C1-4F45-898E-73130A6EE3EC}"/>
     <cellStyle name="Millares [0] 2 2 3" xfId="1329" xr:uid="{3B2564A1-BEFA-49AD-B6BB-07FEA5FEE5AE}"/>
+    <cellStyle name="Millares [0] 2 2 3 2" xfId="4181" xr:uid="{2B00D76B-CDBB-4AA5-BC3A-378293F8CBA3}"/>
     <cellStyle name="Millares [0] 2 2 4" xfId="1330" xr:uid="{DB25AE86-F06F-441D-90FE-673EC7D4371C}"/>
+    <cellStyle name="Millares [0] 2 2 4 2" xfId="4182" xr:uid="{FA362784-1434-4028-AFC7-8F55A513A3F0}"/>
     <cellStyle name="Millares [0] 2 2 5" xfId="1331" xr:uid="{6607FFF7-E875-4BB5-BAA2-EEE87833FCCA}"/>
+    <cellStyle name="Millares [0] 2 2 5 2" xfId="4183" xr:uid="{A0E61C2C-06A4-4024-B8DF-CFA6819912AB}"/>
     <cellStyle name="Millares [0] 2 2 6" xfId="1332" xr:uid="{23C4334C-CA33-43FA-B5C4-CDD1D089E3CA}"/>
+    <cellStyle name="Millares [0] 2 2 6 2" xfId="4184" xr:uid="{82386FB0-C2B4-4FB1-85BE-E6FE790ABF98}"/>
     <cellStyle name="Millares [0] 2 2 7" xfId="1333" xr:uid="{000EB771-07A1-4163-B309-B59BF1A3299C}"/>
+    <cellStyle name="Millares [0] 2 2 7 2" xfId="4185" xr:uid="{B203AC87-5830-4852-981C-4F1E4EA579F3}"/>
     <cellStyle name="Millares [0] 2 2 8" xfId="1334" xr:uid="{AC22081E-0B21-4BA1-BAD3-EBB7E7F2FA11}"/>
+    <cellStyle name="Millares [0] 2 2 8 2" xfId="4186" xr:uid="{A4BBC641-8E34-4556-A633-8934E7FE00B8}"/>
     <cellStyle name="Millares [0] 2 3" xfId="1335" xr:uid="{88A6E8B5-32AD-4421-BD30-80890F6F9097}"/>
     <cellStyle name="Millares [0] 2 4" xfId="1336" xr:uid="{9CC6F8D6-1B42-4011-88DE-C210A6B6BE18}"/>
     <cellStyle name="Millares [0] 2 4 2" xfId="1337" xr:uid="{B99A6AAF-432C-4EE9-BA1A-78E14F833CBE}"/>
+    <cellStyle name="Millares [0] 2 4 2 2" xfId="4188" xr:uid="{E29A6A48-2978-4B34-9ACD-097AEA5BEE8D}"/>
     <cellStyle name="Millares [0] 2 4 3" xfId="1338" xr:uid="{115D5829-5C2D-4FC2-8A13-8CFEF0AF26FA}"/>
     <cellStyle name="Millares [0] 2 4 3 2" xfId="1339" xr:uid="{EB4EA711-31FA-4787-AECA-687EF3AA1EB8}"/>
+    <cellStyle name="Millares [0] 2 4 3 2 2" xfId="4190" xr:uid="{0D412552-2533-4C67-A9AF-87FA5651E59D}"/>
+    <cellStyle name="Millares [0] 2 4 3 3" xfId="4189" xr:uid="{5E546DB9-F039-4CD1-B68E-3475F9BD887C}"/>
     <cellStyle name="Millares [0] 2 4 4" xfId="1340" xr:uid="{0AAB2999-885A-4784-B5D1-E5A9BD624DAA}"/>
     <cellStyle name="Millares [0] 2 4 4 2" xfId="1341" xr:uid="{7B5264B3-A853-4088-88C9-E8D4F0E2425B}"/>
+    <cellStyle name="Millares [0] 2 4 4 2 2" xfId="4192" xr:uid="{E171F6DA-E42C-4D48-B4ED-D7FDC69B43A3}"/>
     <cellStyle name="Millares [0] 2 4 4 3" xfId="1342" xr:uid="{A41B7A7C-352C-4105-B80A-67E397DFC30F}"/>
+    <cellStyle name="Millares [0] 2 4 4 3 2" xfId="4193" xr:uid="{D60879EC-9C88-4D3E-8D79-B9161193F0C8}"/>
+    <cellStyle name="Millares [0] 2 4 4 4" xfId="4191" xr:uid="{2C626C2D-DFF9-480E-994A-3F4B9B66F57A}"/>
     <cellStyle name="Millares [0] 2 4 5" xfId="1343" xr:uid="{D147CC2A-6E03-4E6B-9F66-8A5C0E0FE3F3}"/>
     <cellStyle name="Millares [0] 2 4 5 2" xfId="1344" xr:uid="{F418CDA9-A721-4BBE-B5B9-42F643237D5B}"/>
+    <cellStyle name="Millares [0] 2 4 5 2 2" xfId="4195" xr:uid="{8B6A5303-0F08-43E9-8BDC-5490F7388628}"/>
     <cellStyle name="Millares [0] 2 4 5 3" xfId="1345" xr:uid="{5E1A3886-89F8-45B5-AC33-859AA34A6804}"/>
+    <cellStyle name="Millares [0] 2 4 5 3 2" xfId="4196" xr:uid="{68C4B40F-84C5-427B-8533-2809B42F2DD0}"/>
+    <cellStyle name="Millares [0] 2 4 5 4" xfId="4194" xr:uid="{AB809BD2-3F07-4973-AC32-838D6AF78A2F}"/>
     <cellStyle name="Millares [0] 2 4 6" xfId="1346" xr:uid="{5E1FC7C4-2821-4F46-83FE-D0067543FE91}"/>
+    <cellStyle name="Millares [0] 2 4 6 2" xfId="4197" xr:uid="{B14DA91F-D6BA-423A-B418-1450FA16C4E8}"/>
+    <cellStyle name="Millares [0] 2 4 7" xfId="4187" xr:uid="{D3DC0532-71DB-49C2-B4FC-47EFD77C43BB}"/>
     <cellStyle name="Millares [0] 2 5" xfId="1347" xr:uid="{29C862E9-77A1-486F-BF54-84718601E8F9}"/>
+    <cellStyle name="Millares [0] 2 5 2" xfId="4198" xr:uid="{4558BEC0-CB09-4F44-8CD7-67B66DD86C24}"/>
     <cellStyle name="Millares [0] 2 6" xfId="1348" xr:uid="{5E920137-CB69-442F-BEE9-93506D9DBA78}"/>
+    <cellStyle name="Millares [0] 2 6 2" xfId="4199" xr:uid="{50B71E5C-AAB8-4B75-8B96-C5D7B5A9D25C}"/>
     <cellStyle name="Millares [0] 2 7" xfId="1349" xr:uid="{9CA4A0D7-6820-4666-ACF4-680F944C3BAE}"/>
+    <cellStyle name="Millares [0] 2 7 2" xfId="4200" xr:uid="{6EA88854-FA24-45F6-925D-0224010783FF}"/>
     <cellStyle name="Millares [0] 2 8" xfId="1350" xr:uid="{FD08FA78-7A2A-4D39-8C48-305B53626123}"/>
+    <cellStyle name="Millares [0] 2 8 2" xfId="4201" xr:uid="{BBFAF65D-5921-4EE9-A877-CC206EFE01F0}"/>
     <cellStyle name="Millares [0] 2 9" xfId="1351" xr:uid="{DB186E2A-97C2-4572-9708-5D0313D2A13C}"/>
+    <cellStyle name="Millares [0] 2 9 2" xfId="4202" xr:uid="{DC8E1FBB-8571-40CB-AF39-311ACCAAE64E}"/>
     <cellStyle name="Millares [0] 3" xfId="1352" xr:uid="{2F1C664F-A067-4FDF-AC2F-DA92A78F89FD}"/>
     <cellStyle name="Millares [0] 4" xfId="1353" xr:uid="{0932EBCC-05C4-4563-AF67-33D1ECC7AC45}"/>
     <cellStyle name="Millares 10" xfId="1354" xr:uid="{7A7B28AB-63EA-40B7-83B6-BE8D6F1AFDA4}"/>
@@ -8755,24 +9159,33 @@
     <cellStyle name="Millares 17 7" xfId="1440" xr:uid="{B1867D44-F39C-4B53-A9E1-341A38FD6E04}"/>
     <cellStyle name="Millares 18" xfId="1441" xr:uid="{62B44F1C-0D5C-4E77-8705-A9AC45518FB4}"/>
     <cellStyle name="Millares 18 2" xfId="1442" xr:uid="{FCFB75F1-0304-47C1-945C-02A061B5A4B7}"/>
+    <cellStyle name="Millares 18 3" xfId="4203" xr:uid="{8C23CDD9-7DF7-400A-BD37-27EEB855987E}"/>
     <cellStyle name="Millares 19" xfId="1443" xr:uid="{1ED48804-3D7A-4979-B7B6-695007BED1AE}"/>
     <cellStyle name="Millares 19 2" xfId="1444" xr:uid="{F0EFC25C-8DD1-4CE0-9165-88C64C4F240E}"/>
+    <cellStyle name="Millares 19 3" xfId="4204" xr:uid="{5A256D4D-B26F-4609-BB68-0352D89CDA02}"/>
     <cellStyle name="Millares 2" xfId="1445" xr:uid="{54643474-2EBB-4720-A879-D92663F7799F}"/>
     <cellStyle name="Millares 2 2" xfId="1446" xr:uid="{EDA917A1-3D26-4346-B1E9-AA2DAAB3366E}"/>
     <cellStyle name="Millares 2 2 2" xfId="1447" xr:uid="{C7983444-7902-4665-B337-B01D74338E3B}"/>
     <cellStyle name="Millares 2 2 2 2" xfId="1448" xr:uid="{FCD83B07-88F6-46DD-9BD8-9AF4559AB28C}"/>
+    <cellStyle name="Millares 2 2 2 2 2" xfId="4206" xr:uid="{8E5A9E57-3A7D-406C-9E14-94863FF10738}"/>
     <cellStyle name="Millares 2 2 3" xfId="1449" xr:uid="{D3C7EA0A-93D7-4D6A-8B91-29F2F67395DF}"/>
     <cellStyle name="Millares 2 3" xfId="1450" xr:uid="{11781031-7EC0-499C-9CD3-6EF9DA8B3C64}"/>
     <cellStyle name="Millares 2 3 2" xfId="1451" xr:uid="{62B255C4-6995-43E8-8E5A-A0390B8C6201}"/>
+    <cellStyle name="Millares 2 3 2 2" xfId="4207" xr:uid="{479BBD59-8E85-4932-A854-5B196CA458DF}"/>
     <cellStyle name="Millares 2 4" xfId="1452" xr:uid="{5A654753-D148-45D5-A1C9-3789B3129ECE}"/>
     <cellStyle name="Millares 2 4 2" xfId="1453" xr:uid="{6FC0605A-2126-4E2E-953E-01843D9A94E7}"/>
     <cellStyle name="Millares 2 5" xfId="1454" xr:uid="{38ED8EE5-D0EE-4780-88B5-9EB292CAE662}"/>
+    <cellStyle name="Millares 2 5 2" xfId="4208" xr:uid="{7626F202-F53F-4112-9E8E-48DDA5895F8D}"/>
     <cellStyle name="Millares 2 6" xfId="1455" xr:uid="{59B33B42-04DD-43A7-82DA-75F427B0C791}"/>
+    <cellStyle name="Millares 2 6 2" xfId="4209" xr:uid="{068DFFFA-2E09-4A01-A953-2B1A05D9083E}"/>
+    <cellStyle name="Millares 2 7" xfId="4205" xr:uid="{EDA37EE2-568A-4AE6-9BA4-A371AC67C84C}"/>
     <cellStyle name="Millares 2_Cap 3 Transacciones v27042009" xfId="1456" xr:uid="{2688650D-0F3A-41E3-BFD0-A24F4C9B58F0}"/>
     <cellStyle name="Millares 20" xfId="1457" xr:uid="{2A762D66-FBB4-44DB-99D9-3293FE30B0FE}"/>
     <cellStyle name="Millares 20 2" xfId="1458" xr:uid="{882D35E2-C0AB-4B3F-8E1B-3A25F5880198}"/>
+    <cellStyle name="Millares 20 3" xfId="4210" xr:uid="{7F326EBB-A413-4179-A300-DDBD8046B487}"/>
     <cellStyle name="Millares 21" xfId="1459" xr:uid="{1A396A2E-7E11-411E-9260-017ACB9FDA5C}"/>
     <cellStyle name="Millares 21 2" xfId="1460" xr:uid="{4602ED5C-0096-49BF-991C-631EA0EEDC5F}"/>
+    <cellStyle name="Millares 21 3" xfId="4211" xr:uid="{DC7EA48F-67DE-47E2-9699-17A63D5A797C}"/>
     <cellStyle name="Millares 22" xfId="1461" xr:uid="{16797636-C34A-4C4F-8DCD-4BEA0C3BDD5D}"/>
     <cellStyle name="Millares 22 2" xfId="1462" xr:uid="{FCF5AEDE-AFE9-47A6-8B34-0D9CF00F53DE}"/>
     <cellStyle name="Millares 22 3" xfId="1463" xr:uid="{D586D9F2-E6F1-4571-8207-D9267B88A420}"/>
@@ -8794,90 +9207,173 @@
     <cellStyle name="Millares 29" xfId="1479" xr:uid="{44769A07-AAAB-4A53-9668-0A66EE454FA5}"/>
     <cellStyle name="Millares 3" xfId="1480" xr:uid="{4D03F3FB-AA6A-4056-969B-5B44C7466014}"/>
     <cellStyle name="Millares 3 10" xfId="1481" xr:uid="{00128BE7-5653-4C33-B7F5-570661B7173F}"/>
+    <cellStyle name="Millares 3 10 2" xfId="4212" xr:uid="{BB8EF208-4295-4508-B565-C215280F7CCA}"/>
     <cellStyle name="Millares 3 11" xfId="1482" xr:uid="{9D11E94B-D4F9-41EE-9411-0E5B596CCC05}"/>
+    <cellStyle name="Millares 3 11 2" xfId="4213" xr:uid="{4BC2DCA2-4D85-4000-A74E-B0AAC1B5E5E4}"/>
     <cellStyle name="Millares 3 12" xfId="1483" xr:uid="{C8065E37-CFEC-4E38-8C10-A80B79E6D0C9}"/>
+    <cellStyle name="Millares 3 12 2" xfId="4214" xr:uid="{A62702CD-8B85-4A1E-B588-439BA95649D3}"/>
     <cellStyle name="Millares 3 13" xfId="1484" xr:uid="{38FF4088-7331-4A7F-B80F-86B4310A799E}"/>
+    <cellStyle name="Millares 3 13 2" xfId="4215" xr:uid="{FB40C6E5-B23A-4DF6-8F19-C26E8B71F467}"/>
     <cellStyle name="Millares 3 2" xfId="1485" xr:uid="{8B614AFC-DA9B-454A-BCCD-5C8E07255479}"/>
     <cellStyle name="Millares 3 2 2" xfId="1486" xr:uid="{F3DFF828-1FBE-4E23-9AA5-0862A0F6E42B}"/>
     <cellStyle name="Millares 3 3" xfId="1487" xr:uid="{521B639B-64E2-42F6-B212-1F01AE24B63F}"/>
+    <cellStyle name="Millares 3 3 10" xfId="4216" xr:uid="{06F2578E-1E80-4175-9771-CB6384EF433C}"/>
     <cellStyle name="Millares 3 3 2" xfId="1488" xr:uid="{040DBF1D-3287-4245-BC4C-4E02AD73B44D}"/>
     <cellStyle name="Millares 3 3 2 2" xfId="1489" xr:uid="{26CECB72-F184-4C14-A789-D6354F709CDA}"/>
+    <cellStyle name="Millares 3 3 2 2 2" xfId="4218" xr:uid="{60AE7D5C-35AC-43A5-9D8A-183427B91BC3}"/>
     <cellStyle name="Millares 3 3 2 3" xfId="1490" xr:uid="{5124E508-812F-4950-87B7-E6329ED4D483}"/>
     <cellStyle name="Millares 3 3 2 3 2" xfId="1491" xr:uid="{6660B833-1369-4AFB-850B-125A5A0BF9A9}"/>
+    <cellStyle name="Millares 3 3 2 3 2 2" xfId="4220" xr:uid="{3AABF42F-B01E-4D15-9071-7A189C79F134}"/>
+    <cellStyle name="Millares 3 3 2 3 3" xfId="4219" xr:uid="{F22E74E7-635D-4BDD-B7B6-30C62FB3E060}"/>
     <cellStyle name="Millares 3 3 2 4" xfId="1492" xr:uid="{EC28CA22-F2DE-4E19-AB4E-416EFFD4B54E}"/>
     <cellStyle name="Millares 3 3 2 4 2" xfId="1493" xr:uid="{8ACC8DD5-98CA-46BF-A913-F538CE71EFFA}"/>
+    <cellStyle name="Millares 3 3 2 4 2 2" xfId="4222" xr:uid="{690B7D73-7059-45E8-9F06-B9B237D557AF}"/>
     <cellStyle name="Millares 3 3 2 4 3" xfId="1494" xr:uid="{A2F643F5-DA8D-4349-BB38-CAAD5351CADE}"/>
+    <cellStyle name="Millares 3 3 2 4 3 2" xfId="4223" xr:uid="{9F495134-E6AF-4A5B-BD8A-2E77537774E0}"/>
+    <cellStyle name="Millares 3 3 2 4 4" xfId="4221" xr:uid="{FA918DB1-2F6D-414E-B6D2-1B1248326BF3}"/>
     <cellStyle name="Millares 3 3 2 5" xfId="1495" xr:uid="{93D73DDC-58F9-4F14-9C56-27051772991B}"/>
     <cellStyle name="Millares 3 3 2 5 2" xfId="1496" xr:uid="{8EB2CFA0-9058-40DF-8AB4-149EFD67FAF9}"/>
+    <cellStyle name="Millares 3 3 2 5 2 2" xfId="4225" xr:uid="{84B575B4-3DE8-4DD5-9CE0-A08D612C9E24}"/>
     <cellStyle name="Millares 3 3 2 5 3" xfId="1497" xr:uid="{9763348B-063C-40DC-B538-42CD05582CDB}"/>
+    <cellStyle name="Millares 3 3 2 5 3 2" xfId="4226" xr:uid="{C6567702-07A7-4C63-9F8F-44C3A020AD1A}"/>
+    <cellStyle name="Millares 3 3 2 5 4" xfId="4224" xr:uid="{3C5C8F15-F8D9-4591-BC2D-0265FAE6CB8F}"/>
     <cellStyle name="Millares 3 3 2 6" xfId="1498" xr:uid="{E993EF80-BA1E-4892-9CBC-6FB846127CCB}"/>
+    <cellStyle name="Millares 3 3 2 6 2" xfId="4227" xr:uid="{CA7306ED-B3B7-4943-BE07-7E7E0BBD31CA}"/>
     <cellStyle name="Millares 3 3 2 7" xfId="1499" xr:uid="{C613BABC-6AB6-425E-BCE4-60A40B3C4CF8}"/>
+    <cellStyle name="Millares 3 3 2 7 2" xfId="4228" xr:uid="{D46BDE81-8950-47D6-89CA-5F1D7AB36482}"/>
     <cellStyle name="Millares 3 3 2 8" xfId="1500" xr:uid="{9B6A4C30-6224-4923-A98C-CFE94C11E46A}"/>
+    <cellStyle name="Millares 3 3 2 8 2" xfId="4229" xr:uid="{207F219C-C295-4EDA-A417-827CB9713D72}"/>
+    <cellStyle name="Millares 3 3 2 9" xfId="4217" xr:uid="{18C43FC3-4069-457D-BC36-1F1F62B85EA5}"/>
     <cellStyle name="Millares 3 3 3" xfId="1501" xr:uid="{DE6246B9-99D4-49A9-90C3-41D4312EB6A7}"/>
+    <cellStyle name="Millares 3 3 3 2" xfId="4230" xr:uid="{EB7656ED-07A5-4D41-9CC0-A6081344DADF}"/>
     <cellStyle name="Millares 3 3 4" xfId="1502" xr:uid="{60F1B9EE-EAFA-4A3A-81A2-7A516D9FB5B2}"/>
     <cellStyle name="Millares 3 3 4 2" xfId="1503" xr:uid="{BB047BCC-BB15-4066-BF5A-1A35BDE5781B}"/>
+    <cellStyle name="Millares 3 3 4 2 2" xfId="4232" xr:uid="{55270B3E-E2FD-48F2-BE19-E08AEDD75111}"/>
+    <cellStyle name="Millares 3 3 4 3" xfId="4231" xr:uid="{1F814D24-358F-46D9-B227-63B3A968861D}"/>
     <cellStyle name="Millares 3 3 5" xfId="1504" xr:uid="{A3978DA8-4F7F-4459-B54C-2F8886C32AD6}"/>
     <cellStyle name="Millares 3 3 5 2" xfId="1505" xr:uid="{02488F94-EFD0-4164-B2AA-A1349DBBB85E}"/>
+    <cellStyle name="Millares 3 3 5 2 2" xfId="4234" xr:uid="{14987851-D991-4C4C-BF48-6CA29026D5B7}"/>
     <cellStyle name="Millares 3 3 5 3" xfId="1506" xr:uid="{1C153ABC-5704-4855-8DFF-70D553EB60D3}"/>
+    <cellStyle name="Millares 3 3 5 3 2" xfId="4235" xr:uid="{CBCCD0EC-28C5-48FB-B66A-A250AA138158}"/>
+    <cellStyle name="Millares 3 3 5 4" xfId="4233" xr:uid="{C485F0D9-66E4-46AF-901F-A1A6A944D0AD}"/>
     <cellStyle name="Millares 3 3 6" xfId="1507" xr:uid="{8FE36064-DD7A-42E5-B96E-0038E586C16F}"/>
     <cellStyle name="Millares 3 3 6 2" xfId="1508" xr:uid="{D1F204AF-E096-492B-BD4C-CF6CAF387B8C}"/>
+    <cellStyle name="Millares 3 3 6 2 2" xfId="4237" xr:uid="{7BF99414-9B65-4074-B659-DB3C9E9FED2A}"/>
     <cellStyle name="Millares 3 3 6 3" xfId="1509" xr:uid="{BF9374B3-6853-4DEC-A505-6D846A390483}"/>
+    <cellStyle name="Millares 3 3 6 3 2" xfId="4238" xr:uid="{648B1AA2-E311-45AF-8249-4B8EF3EDA80D}"/>
+    <cellStyle name="Millares 3 3 6 4" xfId="4236" xr:uid="{CC1ADE73-CF2F-4536-9E9D-D9408C52DF8D}"/>
     <cellStyle name="Millares 3 3 7" xfId="1510" xr:uid="{1FB5F7D0-62EF-45A7-B191-E699572BB094}"/>
+    <cellStyle name="Millares 3 3 7 2" xfId="4239" xr:uid="{DACF14EA-E0CB-4CCF-ADC4-6078F96A3BE0}"/>
     <cellStyle name="Millares 3 3 8" xfId="1511" xr:uid="{FF2C768E-CA1C-45E3-933D-EF98AAC407DC}"/>
+    <cellStyle name="Millares 3 3 8 2" xfId="4240" xr:uid="{ACDAFAD9-BEA7-4A47-BFDA-CD0637737BDA}"/>
     <cellStyle name="Millares 3 3 9" xfId="1512" xr:uid="{F9419849-0F03-4DFD-9824-3AB83E62D268}"/>
+    <cellStyle name="Millares 3 3 9 2" xfId="4241" xr:uid="{ACAE1260-95AE-434D-931C-26B4DD8747A1}"/>
     <cellStyle name="Millares 3 4" xfId="1513" xr:uid="{F9EDB776-8D77-406F-B257-5FE9408575FC}"/>
+    <cellStyle name="Millares 3 4 10" xfId="4242" xr:uid="{BAF0C2DF-0C17-4942-922E-C7BBCF4E1CC0}"/>
     <cellStyle name="Millares 3 4 2" xfId="1514" xr:uid="{007304FE-8B59-4004-BBCF-3D27C1A96B2C}"/>
     <cellStyle name="Millares 3 4 2 2" xfId="1515" xr:uid="{99A49E87-34FC-4CEC-AA60-BF2D9D7AABFB}"/>
+    <cellStyle name="Millares 3 4 2 2 2" xfId="4244" xr:uid="{A84B8E88-228D-4359-901D-953DE86D3D4E}"/>
     <cellStyle name="Millares 3 4 2 3" xfId="1516" xr:uid="{C4115C01-C914-4CE2-BC60-A4AF4729FB73}"/>
     <cellStyle name="Millares 3 4 2 3 2" xfId="1517" xr:uid="{5806E473-798A-4861-9706-21A96BAF5C95}"/>
+    <cellStyle name="Millares 3 4 2 3 2 2" xfId="4246" xr:uid="{97AD595A-018D-46AF-B5E6-D86A567B7F66}"/>
+    <cellStyle name="Millares 3 4 2 3 3" xfId="4245" xr:uid="{A44BF8E6-117A-428C-BC0E-6C715D950D09}"/>
     <cellStyle name="Millares 3 4 2 4" xfId="1518" xr:uid="{7BD2130A-2791-49C2-B4DA-805E03F3339D}"/>
     <cellStyle name="Millares 3 4 2 4 2" xfId="1519" xr:uid="{2D054C11-FB7A-4C39-BD22-F9B694F36698}"/>
+    <cellStyle name="Millares 3 4 2 4 2 2" xfId="4248" xr:uid="{1151E613-274D-4698-94BD-2481A12ECCE3}"/>
     <cellStyle name="Millares 3 4 2 4 3" xfId="1520" xr:uid="{A7ABFB25-28E3-4E80-B810-5D9100355087}"/>
+    <cellStyle name="Millares 3 4 2 4 3 2" xfId="4249" xr:uid="{EA57CE8A-9888-41A2-A383-71B2B4457AE0}"/>
+    <cellStyle name="Millares 3 4 2 4 4" xfId="4247" xr:uid="{9A7300E0-E4E0-41C5-A85F-3F044A55D5F3}"/>
     <cellStyle name="Millares 3 4 2 5" xfId="1521" xr:uid="{C4B0010C-0099-4447-9AB4-047850FB93B5}"/>
     <cellStyle name="Millares 3 4 2 5 2" xfId="1522" xr:uid="{72FBFA46-65D6-4156-8A6B-83F784A91313}"/>
+    <cellStyle name="Millares 3 4 2 5 2 2" xfId="4251" xr:uid="{DC15A306-9AB2-4894-85FA-849FC6108A7B}"/>
     <cellStyle name="Millares 3 4 2 5 3" xfId="1523" xr:uid="{A2699C65-5F13-4BDD-B507-E576F8486403}"/>
+    <cellStyle name="Millares 3 4 2 5 3 2" xfId="4252" xr:uid="{8AD0214C-735C-4413-82DE-A735242CA1C5}"/>
+    <cellStyle name="Millares 3 4 2 5 4" xfId="4250" xr:uid="{92F15FE1-E7E5-4F20-994D-36B3AEE69217}"/>
     <cellStyle name="Millares 3 4 2 6" xfId="1524" xr:uid="{1C5C22B6-D5AC-4373-9CFC-9425D610AAA7}"/>
+    <cellStyle name="Millares 3 4 2 6 2" xfId="4253" xr:uid="{84077513-458A-40FC-838B-1DD0750B6BA0}"/>
     <cellStyle name="Millares 3 4 2 7" xfId="1525" xr:uid="{2096AC3A-AC03-4B82-980F-3D1C4A463B09}"/>
+    <cellStyle name="Millares 3 4 2 7 2" xfId="4254" xr:uid="{4DBB5910-D888-4C4C-9BC2-6B6BBE2FBC27}"/>
     <cellStyle name="Millares 3 4 2 8" xfId="1526" xr:uid="{EC54B1BC-F7EC-45BC-AD8D-746877E57702}"/>
+    <cellStyle name="Millares 3 4 2 8 2" xfId="4255" xr:uid="{86E5D9BE-33E6-4E9C-ABF0-BA4C70601DE5}"/>
+    <cellStyle name="Millares 3 4 2 9" xfId="4243" xr:uid="{59B150E0-F911-4751-8993-8A9ABE9CE843}"/>
     <cellStyle name="Millares 3 4 3" xfId="1527" xr:uid="{3252119A-2897-40D0-9B4A-B1F1A095AC47}"/>
+    <cellStyle name="Millares 3 4 3 2" xfId="4256" xr:uid="{E5A0D5DD-EDE6-4DEE-9C12-1C6C8DA80168}"/>
     <cellStyle name="Millares 3 4 4" xfId="1528" xr:uid="{84DE0316-DB60-4FE3-B089-DC9437F3E9F6}"/>
     <cellStyle name="Millares 3 4 4 2" xfId="1529" xr:uid="{C7C2FDA6-CA60-48C0-A9A9-5867FB253052}"/>
+    <cellStyle name="Millares 3 4 4 2 2" xfId="4258" xr:uid="{8885DBE9-7CA7-44AF-8D7D-679E6C78247E}"/>
+    <cellStyle name="Millares 3 4 4 3" xfId="4257" xr:uid="{F52C564C-9894-49E9-AD4D-62EB5E1D66CC}"/>
     <cellStyle name="Millares 3 4 5" xfId="1530" xr:uid="{BB3A1AFC-6CC6-40BC-8E3B-9373D2BD9E41}"/>
     <cellStyle name="Millares 3 4 5 2" xfId="1531" xr:uid="{84B14C7E-A8DF-4FF6-832E-DB10703A7C29}"/>
+    <cellStyle name="Millares 3 4 5 2 2" xfId="4260" xr:uid="{3E60ACB7-2FC6-4F64-B545-667E3D0B7E8B}"/>
     <cellStyle name="Millares 3 4 5 3" xfId="1532" xr:uid="{D0A5194C-FD2F-42F3-9B66-63800998F5D6}"/>
+    <cellStyle name="Millares 3 4 5 3 2" xfId="4261" xr:uid="{C4A7C9B0-A0CC-4341-A810-DA2E357C70CC}"/>
+    <cellStyle name="Millares 3 4 5 4" xfId="4259" xr:uid="{2E64ADD2-4AFF-4471-B032-3A1A790B4EBD}"/>
     <cellStyle name="Millares 3 4 6" xfId="1533" xr:uid="{72129748-9884-4FC9-8AA0-8DE656206269}"/>
     <cellStyle name="Millares 3 4 6 2" xfId="1534" xr:uid="{7A7941A9-0A54-449F-AE93-626F9E5DDC61}"/>
+    <cellStyle name="Millares 3 4 6 2 2" xfId="4263" xr:uid="{45E97DC8-2149-40A0-A47C-A525A0660F64}"/>
     <cellStyle name="Millares 3 4 6 3" xfId="1535" xr:uid="{EF488113-A5AE-4987-98EA-6454885D052C}"/>
+    <cellStyle name="Millares 3 4 6 3 2" xfId="4264" xr:uid="{4C3C49B3-11D9-4992-9828-EC4345B0A707}"/>
+    <cellStyle name="Millares 3 4 6 4" xfId="4262" xr:uid="{B0687C85-A38C-48E1-A18C-9DC86BBFA147}"/>
     <cellStyle name="Millares 3 4 7" xfId="1536" xr:uid="{C33E1583-F2E4-4141-B092-4B3295B4014D}"/>
+    <cellStyle name="Millares 3 4 7 2" xfId="4265" xr:uid="{9ACC5171-B468-4755-B326-06D758B1A5D7}"/>
     <cellStyle name="Millares 3 4 8" xfId="1537" xr:uid="{B311A27A-834B-409B-90BB-49F543A53A11}"/>
+    <cellStyle name="Millares 3 4 8 2" xfId="4266" xr:uid="{BCF3A00F-D435-48A2-9DDF-F338343E8EC8}"/>
     <cellStyle name="Millares 3 4 9" xfId="1538" xr:uid="{DFA3F00A-54F4-46F2-8B1F-890C41854122}"/>
+    <cellStyle name="Millares 3 4 9 2" xfId="4267" xr:uid="{B3920D2B-706D-4FFB-98F6-D9946B9761A9}"/>
     <cellStyle name="Millares 3 5" xfId="1539" xr:uid="{316802DF-6D99-468A-8884-6BB3C9D45BC0}"/>
     <cellStyle name="Millares 3 5 2" xfId="1540" xr:uid="{BBBA10E9-7F9D-4EB8-AA8B-D5F2078697C3}"/>
+    <cellStyle name="Millares 3 5 2 2" xfId="4269" xr:uid="{8B79540F-567B-4C53-B0EA-9BFC8266235D}"/>
     <cellStyle name="Millares 3 5 3" xfId="1541" xr:uid="{DA5FE2ED-F94F-48C7-B309-D2EE5E8A385E}"/>
     <cellStyle name="Millares 3 5 3 2" xfId="1542" xr:uid="{F8DCF6F4-03AB-4749-83FA-C18AFD261488}"/>
+    <cellStyle name="Millares 3 5 3 2 2" xfId="4271" xr:uid="{1499A3C5-2230-4D67-846C-8827D2D6AF92}"/>
+    <cellStyle name="Millares 3 5 3 3" xfId="4270" xr:uid="{D3C628D6-B4BC-4B24-87A7-62AC31980DDF}"/>
     <cellStyle name="Millares 3 5 4" xfId="1543" xr:uid="{F74BCDC3-659F-484B-87EF-DBEC2E08CC31}"/>
     <cellStyle name="Millares 3 5 4 2" xfId="1544" xr:uid="{B4E64636-4085-47C6-BAA3-818A1B80B2D1}"/>
+    <cellStyle name="Millares 3 5 4 2 2" xfId="4273" xr:uid="{237E12A8-1265-435E-89E3-1700B5D1F490}"/>
     <cellStyle name="Millares 3 5 4 3" xfId="1545" xr:uid="{5ABA8DBF-3423-467E-969A-00045E0108CE}"/>
+    <cellStyle name="Millares 3 5 4 3 2" xfId="4274" xr:uid="{944A7ACC-4DDC-49AC-8335-008A6C58CB3D}"/>
+    <cellStyle name="Millares 3 5 4 4" xfId="4272" xr:uid="{8D9B9659-A9DD-48DD-BF17-7C8F50226D42}"/>
     <cellStyle name="Millares 3 5 5" xfId="1546" xr:uid="{7449F11F-907A-442D-A017-431B9605FB17}"/>
     <cellStyle name="Millares 3 5 5 2" xfId="1547" xr:uid="{53CC2BA0-5066-4673-9339-604018D62D80}"/>
+    <cellStyle name="Millares 3 5 5 2 2" xfId="4276" xr:uid="{B619604C-97F3-4623-B5DC-157E524F412F}"/>
     <cellStyle name="Millares 3 5 5 3" xfId="1548" xr:uid="{4EF9645E-A472-4B7F-BBE3-CE3E1AD5C34C}"/>
+    <cellStyle name="Millares 3 5 5 3 2" xfId="4277" xr:uid="{4CB585D8-541B-4487-9CDC-96F936EFD5DE}"/>
+    <cellStyle name="Millares 3 5 5 4" xfId="4275" xr:uid="{EC78F1FB-65C1-4ECB-8897-87500BF1D1F8}"/>
     <cellStyle name="Millares 3 5 6" xfId="1549" xr:uid="{05DDB52D-57D9-4889-909B-939A12C9C25E}"/>
+    <cellStyle name="Millares 3 5 6 2" xfId="4278" xr:uid="{D70B5534-1D37-4D1F-864B-1B6226ED440E}"/>
     <cellStyle name="Millares 3 5 7" xfId="1550" xr:uid="{0465949F-BE4C-440A-920E-B4A796BF41C9}"/>
+    <cellStyle name="Millares 3 5 7 2" xfId="4279" xr:uid="{96C76FD8-3291-45C4-BFA8-FE0C6A85F534}"/>
     <cellStyle name="Millares 3 5 8" xfId="1551" xr:uid="{06D84F1F-8E84-4FD0-82CF-FD35BC4ED9BC}"/>
+    <cellStyle name="Millares 3 5 8 2" xfId="4280" xr:uid="{58FD0882-A7D2-4188-8041-C0578B406ACB}"/>
+    <cellStyle name="Millares 3 5 9" xfId="4268" xr:uid="{A4669200-2F91-418E-BEFD-4F4DA2AC9A35}"/>
     <cellStyle name="Millares 3 6" xfId="1552" xr:uid="{DD8447E3-2094-4B8E-A79E-3CFE49221C2F}"/>
+    <cellStyle name="Millares 3 6 2" xfId="4281" xr:uid="{3658FC5F-C6BF-4FE5-B1F2-578840AB042B}"/>
     <cellStyle name="Millares 3 7" xfId="1553" xr:uid="{DBF5672C-87DF-4B79-8A60-2769D6014559}"/>
     <cellStyle name="Millares 3 7 2" xfId="1554" xr:uid="{DAE043E5-AA8F-4CB1-B91D-DF3616AF79DA}"/>
+    <cellStyle name="Millares 3 7 2 2" xfId="4283" xr:uid="{9E7478DF-0EA8-44AE-BE17-1E3DC1E02736}"/>
     <cellStyle name="Millares 3 7 3" xfId="1555" xr:uid="{EE2FA235-E27E-4AE3-B1B0-5236EFF340A3}"/>
     <cellStyle name="Millares 3 7 3 2" xfId="1556" xr:uid="{D8C78970-FB86-4527-B06B-BEDE0CA0A097}"/>
+    <cellStyle name="Millares 3 7 3 2 2" xfId="4285" xr:uid="{174ED960-D191-4FA9-A590-487D9AB22DF5}"/>
+    <cellStyle name="Millares 3 7 3 3" xfId="4284" xr:uid="{07571917-0B52-48A6-86B9-6B8F89E683BA}"/>
     <cellStyle name="Millares 3 7 4" xfId="1557" xr:uid="{2FE7C864-EDF7-488E-B79C-EC7DD58AAE2C}"/>
     <cellStyle name="Millares 3 7 4 2" xfId="1558" xr:uid="{5690FF79-5C34-426D-BE5D-BA7D2DFD4F8C}"/>
+    <cellStyle name="Millares 3 7 4 2 2" xfId="4287" xr:uid="{78CE2880-D00D-4D4E-9748-B2EEFFE7E1FB}"/>
     <cellStyle name="Millares 3 7 4 3" xfId="1559" xr:uid="{195B8360-3424-462F-B87A-D0FEC20C0BDE}"/>
+    <cellStyle name="Millares 3 7 4 3 2" xfId="4288" xr:uid="{7F7A88E3-18C0-40ED-B776-9A47F693A446}"/>
+    <cellStyle name="Millares 3 7 4 4" xfId="4286" xr:uid="{520E59BE-0F03-4C3D-B374-5577DFF84753}"/>
     <cellStyle name="Millares 3 7 5" xfId="1560" xr:uid="{B5957A9E-51C5-445F-8070-B33923ED55ED}"/>
     <cellStyle name="Millares 3 7 5 2" xfId="1561" xr:uid="{16B4871E-E09C-495F-AA78-0ACB4E5A940E}"/>
+    <cellStyle name="Millares 3 7 5 2 2" xfId="4290" xr:uid="{97E8B52D-7E3F-4F2F-8358-863E7414F38B}"/>
     <cellStyle name="Millares 3 7 5 3" xfId="1562" xr:uid="{138A8C12-4980-4100-A9B1-05B8FD4ABAFA}"/>
+    <cellStyle name="Millares 3 7 5 3 2" xfId="4291" xr:uid="{47F5FE00-0743-4308-BD77-D5A189BB6F96}"/>
+    <cellStyle name="Millares 3 7 5 4" xfId="4289" xr:uid="{AB1660E8-2BEA-4AE7-9450-C90A06EBD10F}"/>
     <cellStyle name="Millares 3 7 6" xfId="1563" xr:uid="{17424E18-B56F-47E5-BD98-442D9E7F4827}"/>
+    <cellStyle name="Millares 3 7 6 2" xfId="4292" xr:uid="{0CDB6E8D-FDA2-4C93-829C-9E6BF8ED9EEF}"/>
+    <cellStyle name="Millares 3 7 7" xfId="4282" xr:uid="{0A5DD6E1-FBB1-41BD-AE83-566D9129FEBB}"/>
     <cellStyle name="Millares 3 8" xfId="1564" xr:uid="{B71DF683-929B-48BA-A79F-A34843ECAC7F}"/>
+    <cellStyle name="Millares 3 8 2" xfId="4293" xr:uid="{2672A373-F63B-44C9-B0D8-F7A613C40506}"/>
     <cellStyle name="Millares 3 9" xfId="1565" xr:uid="{3E7C219B-FAFF-4D3A-880A-D7E3DC336BE6}"/>
+    <cellStyle name="Millares 3 9 2" xfId="4294" xr:uid="{AE2D61B6-0A9C-4C71-877F-FE7D777E17BC}"/>
     <cellStyle name="Millares 30" xfId="1566" xr:uid="{34486ABC-3A1F-4E2A-903F-97515F43A4F4}"/>
     <cellStyle name="Millares 31" xfId="1567" xr:uid="{7CB78410-5FC3-4C5B-B6EF-9F6E7534AB98}"/>
     <cellStyle name="Millares 32" xfId="1568" xr:uid="{66DEB894-10E1-4A74-A57D-3130FD563D6C}"/>
@@ -8888,79 +9384,132 @@
     <cellStyle name="Millares 37" xfId="1573" xr:uid="{996B6DA2-D8F9-47FC-B89C-55BC2BA37E2C}"/>
     <cellStyle name="Millares 38" xfId="1574" xr:uid="{B5CF9DEA-D6F2-4B2F-9B03-672691D66842}"/>
     <cellStyle name="Millares 39" xfId="1575" xr:uid="{0DA65C91-79A5-475D-9490-D899102C5607}"/>
+    <cellStyle name="Millares 39 10" xfId="4295" xr:uid="{D7E5215A-54BF-4D75-BA8B-3698E98EAEA3}"/>
     <cellStyle name="Millares 39 2" xfId="1576" xr:uid="{4EE10042-D70B-4462-A61A-149DB4881DF0}"/>
     <cellStyle name="Millares 39 2 2" xfId="1577" xr:uid="{453DF185-9138-4D01-B6F5-0E4DD9C414C0}"/>
+    <cellStyle name="Millares 39 2 2 2" xfId="4297" xr:uid="{76336D88-F46A-491C-8AF1-7C835D2677F5}"/>
     <cellStyle name="Millares 39 2 3" xfId="1578" xr:uid="{F8AC6593-15E9-4FCA-AE7E-D4DE63492F60}"/>
     <cellStyle name="Millares 39 2 3 2" xfId="1579" xr:uid="{52449093-A0E8-4506-96FD-0A3B3BC417AC}"/>
+    <cellStyle name="Millares 39 2 3 2 2" xfId="4299" xr:uid="{C5AC9450-6215-41DF-BFE3-7419A4EE27F3}"/>
+    <cellStyle name="Millares 39 2 3 3" xfId="4298" xr:uid="{2357D7AF-9151-4274-A751-0244C712113A}"/>
     <cellStyle name="Millares 39 2 4" xfId="1580" xr:uid="{79AE57E5-8A65-4D13-94A5-77F7946542D0}"/>
     <cellStyle name="Millares 39 2 4 2" xfId="1581" xr:uid="{AF4868EE-33B2-4E13-87C7-F6A82B72BF45}"/>
+    <cellStyle name="Millares 39 2 4 2 2" xfId="4301" xr:uid="{79E72F94-DB0F-43AF-B983-5E936A46B6EB}"/>
     <cellStyle name="Millares 39 2 4 3" xfId="1582" xr:uid="{725A1E69-940A-48BB-935F-B6BDB595ECBB}"/>
+    <cellStyle name="Millares 39 2 4 3 2" xfId="4302" xr:uid="{51FEBA68-C02A-45BF-AAD5-E275951ABB65}"/>
+    <cellStyle name="Millares 39 2 4 4" xfId="4300" xr:uid="{15DBB556-C6A3-44C1-9DA7-B22F67825A59}"/>
     <cellStyle name="Millares 39 2 5" xfId="1583" xr:uid="{5B90B26E-3804-4C1E-B763-BA3BC03746FA}"/>
     <cellStyle name="Millares 39 2 5 2" xfId="1584" xr:uid="{C83864BA-3770-459C-B0B1-638D1FBA1A53}"/>
+    <cellStyle name="Millares 39 2 5 2 2" xfId="4304" xr:uid="{BE0A71DA-D5C8-40AD-8D23-EF8B3EE7BEEE}"/>
     <cellStyle name="Millares 39 2 5 3" xfId="1585" xr:uid="{2FF8B74F-F609-4194-84BB-EBDF7F8E8719}"/>
+    <cellStyle name="Millares 39 2 5 3 2" xfId="4305" xr:uid="{D4A79CAA-9082-4B93-AB2B-7C0F42E81399}"/>
+    <cellStyle name="Millares 39 2 5 4" xfId="4303" xr:uid="{5554D538-3E99-4B46-BF2E-A094A3287CE2}"/>
     <cellStyle name="Millares 39 2 6" xfId="1586" xr:uid="{46C347C4-AB5A-447C-9CDE-42E1E4905DB3}"/>
+    <cellStyle name="Millares 39 2 6 2" xfId="4306" xr:uid="{9CC7718F-2302-44AC-B27F-6BF3FA7F969F}"/>
     <cellStyle name="Millares 39 2 7" xfId="1587" xr:uid="{3C0AD2FA-B277-42D7-BAF3-EA7A011C91EA}"/>
+    <cellStyle name="Millares 39 2 7 2" xfId="4307" xr:uid="{CD3DEC6B-5DAC-44B6-A9BA-6DE9DC300583}"/>
     <cellStyle name="Millares 39 2 8" xfId="1588" xr:uid="{035C102A-38CF-407E-A720-600118FBC2A7}"/>
+    <cellStyle name="Millares 39 2 8 2" xfId="4308" xr:uid="{2A0B77B1-7CBF-43CA-991A-F9FF8E2F09D1}"/>
+    <cellStyle name="Millares 39 2 9" xfId="4296" xr:uid="{EF2BEFB5-183E-4810-8601-53C610EAEC6E}"/>
     <cellStyle name="Millares 39 3" xfId="1589" xr:uid="{09387C1B-547D-4984-AB09-A390B69D21CC}"/>
+    <cellStyle name="Millares 39 3 2" xfId="4309" xr:uid="{DC905FE4-E445-47CE-A293-08FD0DB35625}"/>
     <cellStyle name="Millares 39 4" xfId="1590" xr:uid="{8B159343-15AB-4798-BB2D-268724062BDB}"/>
     <cellStyle name="Millares 39 4 2" xfId="1591" xr:uid="{A126E819-1527-455D-B6BB-C9AE4A9A6FA1}"/>
+    <cellStyle name="Millares 39 4 2 2" xfId="4311" xr:uid="{88B5A1F9-BBCE-4016-8D36-C6E9A1C7AF20}"/>
+    <cellStyle name="Millares 39 4 3" xfId="4310" xr:uid="{44F19E0A-99FC-4A22-AD03-D82ED7E6A307}"/>
     <cellStyle name="Millares 39 5" xfId="1592" xr:uid="{C1930CC9-590E-4C91-8B4C-5334423C6DE7}"/>
     <cellStyle name="Millares 39 5 2" xfId="1593" xr:uid="{12DE3769-E50E-4B6C-B5F1-D8FFA6A38E36}"/>
+    <cellStyle name="Millares 39 5 2 2" xfId="4313" xr:uid="{9C4F5C5A-DF2B-4CDE-A5A1-A7B45B3AD87B}"/>
     <cellStyle name="Millares 39 5 3" xfId="1594" xr:uid="{E90BC4AF-18EB-4162-B314-32EBED8B6B19}"/>
+    <cellStyle name="Millares 39 5 3 2" xfId="4314" xr:uid="{E1C4A33E-BA64-4D24-BE2E-BB567D8E340D}"/>
+    <cellStyle name="Millares 39 5 4" xfId="4312" xr:uid="{83FF52EB-8CEE-4FBD-B96D-CB8971C73428}"/>
     <cellStyle name="Millares 39 6" xfId="1595" xr:uid="{3CE4623A-C208-45F5-ABD4-ED2D243B91E4}"/>
     <cellStyle name="Millares 39 6 2" xfId="1596" xr:uid="{D47498EE-EE23-4265-9FD9-EF576505AA58}"/>
+    <cellStyle name="Millares 39 6 2 2" xfId="4316" xr:uid="{0CEEC29E-8949-4209-9FF6-69284960A136}"/>
     <cellStyle name="Millares 39 6 3" xfId="1597" xr:uid="{F6AADB22-5488-442E-BA3D-32B1D07B9057}"/>
+    <cellStyle name="Millares 39 6 3 2" xfId="4317" xr:uid="{EB5594F8-B67C-4DEC-B3F7-D2A8445C37C6}"/>
+    <cellStyle name="Millares 39 6 4" xfId="4315" xr:uid="{C878FE82-0C29-4887-AF7C-13C2CBBB0827}"/>
     <cellStyle name="Millares 39 7" xfId="1598" xr:uid="{01AC4CFA-6A4B-4EA6-92F5-6FCD1B8FA087}"/>
+    <cellStyle name="Millares 39 7 2" xfId="4318" xr:uid="{339A4EA5-5218-4D7A-AC3D-6D292D84C6F7}"/>
     <cellStyle name="Millares 39 8" xfId="1599" xr:uid="{5C50FC8E-3A53-4022-A7C3-3062FFF6A33A}"/>
+    <cellStyle name="Millares 39 8 2" xfId="4319" xr:uid="{4F6D9325-4644-48B3-B3DA-3A6035F44D88}"/>
     <cellStyle name="Millares 39 9" xfId="1600" xr:uid="{4EF4C6D0-8714-4611-A3FF-14AF44738A5E}"/>
+    <cellStyle name="Millares 39 9 2" xfId="4320" xr:uid="{08DC534F-9CAB-44B2-A61F-5B3F89043C67}"/>
     <cellStyle name="Millares 4" xfId="1601" xr:uid="{AAF3CC75-CEC4-4682-89FA-A4607AD63C9A}"/>
     <cellStyle name="Millares 4 2" xfId="1602" xr:uid="{920AA470-AF40-4CBA-92FA-13B5FB4EDD4D}"/>
     <cellStyle name="Millares 4 3" xfId="1603" xr:uid="{3CFA6E15-C17F-4246-A34A-DF6DC80F9C62}"/>
     <cellStyle name="Millares 4 4" xfId="1604" xr:uid="{D4DBBCB0-E4BD-43D4-9970-B1AE379F9545}"/>
     <cellStyle name="Millares 40" xfId="1605" xr:uid="{EAC0BDD5-5F54-4FD7-A7C5-8A2DD4A22289}"/>
+    <cellStyle name="Millares 40 2" xfId="4321" xr:uid="{008D3E41-5445-429D-AB2E-F9E7BEBF027A}"/>
     <cellStyle name="Millares 41" xfId="1606" xr:uid="{FECE6749-1096-4C94-ACF7-6D839E7F4E94}"/>
+    <cellStyle name="Millares 41 2" xfId="4322" xr:uid="{8003204A-C6DB-4E0B-B1CF-FDC2B4C4EB2C}"/>
     <cellStyle name="Millares 42" xfId="1607" xr:uid="{DBD56C4F-B80E-4E1D-A062-B79D647E8B8C}"/>
     <cellStyle name="Millares 42 2" xfId="1608" xr:uid="{87509F42-5279-4E03-B9D7-BBAED948823C}"/>
     <cellStyle name="Millares 42 3" xfId="1609" xr:uid="{01315131-2105-4534-86A9-E2D0954556C8}"/>
+    <cellStyle name="Millares 42 3 2" xfId="4324" xr:uid="{99D0B97D-B9A6-4A7E-9807-56C9F19AE3B6}"/>
+    <cellStyle name="Millares 42 4" xfId="4323" xr:uid="{5A3C1E94-18DB-4B56-BBAD-8AC099E3F8F2}"/>
     <cellStyle name="Millares 43" xfId="1610" xr:uid="{058E9CFD-309E-4841-A79D-5A77515793D9}"/>
     <cellStyle name="Millares 43 2" xfId="1611" xr:uid="{19E89880-6B51-4927-95B2-72E3E8C0E021}"/>
     <cellStyle name="Millares 43 3" xfId="1612" xr:uid="{783F5BDE-66C9-4455-AA64-B4248D65C4BF}"/>
+    <cellStyle name="Millares 43 3 2" xfId="4326" xr:uid="{09ED6B8A-9DEF-4A45-95DD-CAE0931CDF45}"/>
+    <cellStyle name="Millares 43 4" xfId="4325" xr:uid="{E454B250-83AC-4A2A-A42C-24B4A50264FD}"/>
     <cellStyle name="Millares 44" xfId="1613" xr:uid="{FF05B5D4-749A-446A-A9D8-AEDEAE0060B8}"/>
     <cellStyle name="Millares 44 2" xfId="1614" xr:uid="{61879465-1EF8-4082-9ECF-47BABC4CBBB0}"/>
     <cellStyle name="Millares 44 3" xfId="1615" xr:uid="{552BC01B-8BF7-46C0-A6DE-0A57BD3C317C}"/>
+    <cellStyle name="Millares 44 3 2" xfId="4328" xr:uid="{CD40D743-9162-4060-BD56-5748A4F35447}"/>
+    <cellStyle name="Millares 44 4" xfId="4327" xr:uid="{4C63BFF9-B4A9-4419-8FDD-0863A2B372ED}"/>
     <cellStyle name="Millares 45" xfId="1616" xr:uid="{1C57CC0B-06FB-4C9D-8480-02F511150669}"/>
     <cellStyle name="Millares 45 2" xfId="1617" xr:uid="{811D3873-2478-450B-8249-67A9D110DF81}"/>
     <cellStyle name="Millares 45 3" xfId="1618" xr:uid="{3BF92481-EBD2-47F3-B4EC-268D6EA3DE9D}"/>
+    <cellStyle name="Millares 45 3 2" xfId="4330" xr:uid="{7132ACEE-4CB0-483E-804C-915E16CA4F63}"/>
+    <cellStyle name="Millares 45 4" xfId="4329" xr:uid="{A0B124DC-596F-4751-A810-6535DCF238ED}"/>
     <cellStyle name="Millares 46" xfId="1619" xr:uid="{D33FBA04-970C-4A69-8AB5-1E852EF2BC4E}"/>
     <cellStyle name="Millares 46 2" xfId="1620" xr:uid="{F6F6FCE6-1506-4F44-A8A3-66C53625F90F}"/>
     <cellStyle name="Millares 46 3" xfId="1621" xr:uid="{9D2DBCAC-FC79-4018-986F-7CED4AA3B8C1}"/>
+    <cellStyle name="Millares 46 3 2" xfId="4332" xr:uid="{41D77C85-2CAA-4F6B-B60B-19FE4B36448C}"/>
+    <cellStyle name="Millares 46 4" xfId="4331" xr:uid="{0724AC4B-7196-4D24-901A-6A81758A177A}"/>
     <cellStyle name="Millares 47" xfId="1622" xr:uid="{0E897464-03B8-4B3F-ADF8-70BEB30CE2BB}"/>
     <cellStyle name="Millares 47 2" xfId="1623" xr:uid="{C48F1CD7-947B-4AFE-8A39-A91DBDB2B785}"/>
     <cellStyle name="Millares 47 3" xfId="1624" xr:uid="{CFDA7725-5953-47DE-9CDE-27DBFBFDBEFC}"/>
+    <cellStyle name="Millares 47 3 2" xfId="4334" xr:uid="{A9B46DA4-DD72-470B-8FBC-CC35ACAE366B}"/>
+    <cellStyle name="Millares 47 4" xfId="4333" xr:uid="{66461527-5E41-407B-88C1-483DC7C0E669}"/>
     <cellStyle name="Millares 48" xfId="1625" xr:uid="{18B5022E-4343-4E43-8860-45948A5FB0DB}"/>
     <cellStyle name="Millares 48 2" xfId="1626" xr:uid="{B58AC618-1B2E-4819-8324-321309B98DC6}"/>
     <cellStyle name="Millares 48 3" xfId="1627" xr:uid="{A16C811C-8D96-4729-BB09-2CF06BC32DA7}"/>
     <cellStyle name="Millares 48 4" xfId="1628" xr:uid="{4397589C-3E3E-483D-B56A-AD09872F5EC7}"/>
     <cellStyle name="Millares 48 5" xfId="1629" xr:uid="{2B77D1B8-4BE0-434B-90EF-35DE43CA00AB}"/>
+    <cellStyle name="Millares 48 5 2" xfId="4336" xr:uid="{448114AB-E41A-4C3C-9B95-FA3065D3ED80}"/>
+    <cellStyle name="Millares 48 6" xfId="4335" xr:uid="{89C87C8A-EF9A-4AC3-B002-84147F3E3456}"/>
     <cellStyle name="Millares 49" xfId="1630" xr:uid="{E1E25909-7C10-49D5-8917-BDA19C455A05}"/>
     <cellStyle name="Millares 49 2" xfId="1631" xr:uid="{ECE86FDF-AB45-4587-80AA-21B4D5547205}"/>
     <cellStyle name="Millares 49 3" xfId="1632" xr:uid="{E5E17593-985C-40BD-A6BC-21AFC27EEC27}"/>
+    <cellStyle name="Millares 49 3 2" xfId="4338" xr:uid="{ACB69BC9-DC1F-4110-B564-59541FC7A309}"/>
+    <cellStyle name="Millares 49 4" xfId="4337" xr:uid="{D7CB45A7-DD45-4A2C-B3A9-2905447AF30C}"/>
     <cellStyle name="Millares 5" xfId="1633" xr:uid="{55C14373-0BA4-4284-958F-E336AE4F3DFF}"/>
     <cellStyle name="Millares 5 2" xfId="1634" xr:uid="{B069EA33-F033-4FB0-B59F-1DB7A879716D}"/>
     <cellStyle name="Millares 5 2 2" xfId="1635" xr:uid="{11A718EE-5E26-40E4-98F8-307A2E2E07C4}"/>
+    <cellStyle name="Millares 5 2 2 2" xfId="4339" xr:uid="{BA33531F-01D1-4C61-80BA-05F81354526E}"/>
     <cellStyle name="Millares 5 3" xfId="1636" xr:uid="{00C0AC70-3D77-4239-BC4B-98D81C3FAC05}"/>
     <cellStyle name="Millares 50" xfId="1637" xr:uid="{4F3BB6F6-0E91-4FC4-97B5-E8351C1EF1A2}"/>
     <cellStyle name="Millares 50 2" xfId="1638" xr:uid="{63FCFA70-4BA4-4F83-8210-742254D939DC}"/>
     <cellStyle name="Millares 50 3" xfId="1639" xr:uid="{0E56AD2B-EA32-4E3C-8B6A-B667047E18EE}"/>
+    <cellStyle name="Millares 50 3 2" xfId="4341" xr:uid="{020C8F2B-95CA-4184-9201-B26646AC017B}"/>
+    <cellStyle name="Millares 50 4" xfId="4340" xr:uid="{7313E847-E257-45D6-A353-B7658D4F2CBE}"/>
     <cellStyle name="Millares 51" xfId="1640" xr:uid="{90E9B751-6771-4C5C-A13E-3DEEE475B223}"/>
     <cellStyle name="Millares 51 2" xfId="1641" xr:uid="{0FC3C159-91D2-4009-B49D-C8B5E75CEA95}"/>
     <cellStyle name="Millares 51 3" xfId="1642" xr:uid="{0DD1A652-D9C4-4433-9571-1AB6CDE348EF}"/>
+    <cellStyle name="Millares 51 3 2" xfId="4343" xr:uid="{2ED3A91F-1E96-4598-8E99-CEFACBE3F73C}"/>
+    <cellStyle name="Millares 51 4" xfId="4342" xr:uid="{F3F2647D-4C0A-42D9-8A82-2DD6DB7E2051}"/>
     <cellStyle name="Millares 52" xfId="1643" xr:uid="{483AE55A-3D9B-42FF-BBE2-45DB51D4F83A}"/>
     <cellStyle name="Millares 52 2" xfId="1644" xr:uid="{AF1FF9A1-0C51-4290-830B-D0DA626C4B7C}"/>
     <cellStyle name="Millares 52 3" xfId="1645" xr:uid="{6253834C-6AE8-481F-9020-E71CA2619069}"/>
+    <cellStyle name="Millares 52 3 2" xfId="4345" xr:uid="{A0F81934-3A52-4FCF-B1F7-ED75F4CB2AD9}"/>
+    <cellStyle name="Millares 52 4" xfId="4344" xr:uid="{99D95D13-1399-4CA4-840D-F616279E19D8}"/>
     <cellStyle name="Millares 53" xfId="1646" xr:uid="{94C06255-A0DF-47F5-9B45-97EB3EEBEE5C}"/>
     <cellStyle name="Millares 53 2" xfId="1647" xr:uid="{D818449B-D9C4-499F-AF15-9030CCFA0E69}"/>
     <cellStyle name="Millares 53 3" xfId="1648" xr:uid="{5838168E-66CB-4D24-975B-05222EB1F6DC}"/>
+    <cellStyle name="Millares 53 3 2" xfId="4347" xr:uid="{1718EBAC-4574-40EE-9B9F-69E6207FD636}"/>
+    <cellStyle name="Millares 53 4" xfId="4346" xr:uid="{9ADAE5E5-C740-46BA-89BD-6078B399098C}"/>
     <cellStyle name="Millares 54" xfId="1649" xr:uid="{54F4D0D0-405C-4668-8085-F8F494BC2540}"/>
     <cellStyle name="Millares 55" xfId="1650" xr:uid="{98D83A02-A3E6-4232-8AC1-9063B7AD0EFD}"/>
     <cellStyle name="Millares 56" xfId="1651" xr:uid="{EF344335-ADA9-4C62-BA70-CEC38E227070}"/>
@@ -8970,30 +9519,56 @@
     <cellStyle name="Millares 6" xfId="1655" xr:uid="{A9F48016-49F8-4E64-8E5E-3A1561E729A5}"/>
     <cellStyle name="Millares 6 2" xfId="1656" xr:uid="{52418B88-FA0A-4C97-BA2E-92ED0BB9554B}"/>
     <cellStyle name="Millares 6 2 2" xfId="1657" xr:uid="{45E5E272-D1E1-42B5-99AC-6797096811B3}"/>
+    <cellStyle name="Millares 6 2 2 2" xfId="4349" xr:uid="{EFFAE613-95CF-4DDD-AE78-CE1EF88E9925}"/>
     <cellStyle name="Millares 6 2 3" xfId="1658" xr:uid="{945C154D-9165-48D5-A22C-6831708F25FB}"/>
     <cellStyle name="Millares 6 2 3 2" xfId="1659" xr:uid="{C22E8432-7E82-4E7C-96C7-C097A8C029BB}"/>
+    <cellStyle name="Millares 6 2 3 2 2" xfId="4351" xr:uid="{8FAF3E99-84AA-429D-A497-B441F6F9F0D4}"/>
+    <cellStyle name="Millares 6 2 3 3" xfId="4350" xr:uid="{D6E1E43C-3D5F-4580-8AB2-DF14572CB9D3}"/>
     <cellStyle name="Millares 6 2 4" xfId="1660" xr:uid="{65539B3F-007D-481A-AC9C-E768830ED3E5}"/>
     <cellStyle name="Millares 6 2 4 2" xfId="1661" xr:uid="{23102F66-4D19-4F95-B7E8-C8666A1D91FE}"/>
+    <cellStyle name="Millares 6 2 4 2 2" xfId="4353" xr:uid="{D0F39647-C61F-4836-93B6-735538E2CAA5}"/>
     <cellStyle name="Millares 6 2 4 3" xfId="1662" xr:uid="{4E0052FD-FFE7-4270-8714-2C5A5B7C0EF0}"/>
+    <cellStyle name="Millares 6 2 4 3 2" xfId="4354" xr:uid="{5B9B7253-15FF-491E-ABD1-C6C91B20F116}"/>
+    <cellStyle name="Millares 6 2 4 4" xfId="4352" xr:uid="{AB3DDD48-CF99-4049-B7BC-5D603A526B55}"/>
     <cellStyle name="Millares 6 2 5" xfId="1663" xr:uid="{C1FC18BA-D6E0-4134-91A4-A173F80E03BF}"/>
     <cellStyle name="Millares 6 2 5 2" xfId="1664" xr:uid="{86221B97-92AB-43EB-8665-292661C5189A}"/>
+    <cellStyle name="Millares 6 2 5 2 2" xfId="4356" xr:uid="{9DCB5B43-3AB7-41CD-B1C0-9F1ADD638210}"/>
     <cellStyle name="Millares 6 2 5 3" xfId="1665" xr:uid="{9E55F84D-9EF2-4E09-8A8B-1A2A1771A818}"/>
+    <cellStyle name="Millares 6 2 5 3 2" xfId="4357" xr:uid="{9BE5794A-04BB-42F8-BDAD-796F243892CA}"/>
+    <cellStyle name="Millares 6 2 5 4" xfId="4355" xr:uid="{161A1153-03A6-4551-84BF-8C2C49E546B4}"/>
     <cellStyle name="Millares 6 2 6" xfId="1666" xr:uid="{72FBEB73-1A7E-4EC1-8867-A5F8608C05D3}"/>
+    <cellStyle name="Millares 6 2 6 2" xfId="4358" xr:uid="{F8261E94-7462-4DB8-BC97-D84249072259}"/>
     <cellStyle name="Millares 6 2 7" xfId="1667" xr:uid="{C13F38D0-4399-40EA-878E-1968FCFD968C}"/>
+    <cellStyle name="Millares 6 2 7 2" xfId="4359" xr:uid="{FCF51966-CB09-4C62-B0DC-70F60AAD8C91}"/>
     <cellStyle name="Millares 6 2 8" xfId="1668" xr:uid="{FB3D7BDA-BCC6-4164-AA60-C5DD76945FF6}"/>
+    <cellStyle name="Millares 6 2 8 2" xfId="4360" xr:uid="{82875DC8-E7FD-41C4-A22A-7A83EB86D5A4}"/>
+    <cellStyle name="Millares 6 2 9" xfId="4348" xr:uid="{32D0CD8F-09BE-474B-B5CA-51EC981A1FF7}"/>
     <cellStyle name="Millares 6 3" xfId="1669" xr:uid="{C5B3B59F-358D-4EC0-A51B-05C757C8AB8D}"/>
     <cellStyle name="Millares 6 3 2" xfId="1670" xr:uid="{8918AAD9-06A7-48DD-9FD6-10EF2E93A711}"/>
+    <cellStyle name="Millares 6 3 2 2" xfId="4362" xr:uid="{0889BA00-8E5F-40AA-96DA-EA66B444BA72}"/>
     <cellStyle name="Millares 6 3 3" xfId="1671" xr:uid="{4350E858-A9D0-4145-A6CF-17A6DBBE0274}"/>
     <cellStyle name="Millares 6 3 3 2" xfId="1672" xr:uid="{24764904-AAFA-4FE1-A356-1E8342978E5F}"/>
+    <cellStyle name="Millares 6 3 3 2 2" xfId="4364" xr:uid="{638B8DE7-2444-4641-8129-0AA671136551}"/>
+    <cellStyle name="Millares 6 3 3 3" xfId="4363" xr:uid="{6187D75F-1AF7-4CA9-BDAD-61DE77C5B65F}"/>
     <cellStyle name="Millares 6 3 4" xfId="1673" xr:uid="{345AA82E-7D2B-44BA-9539-515F2D0DCBC1}"/>
     <cellStyle name="Millares 6 3 4 2" xfId="1674" xr:uid="{AC0806E4-8EFF-4D87-A814-C9376CED287D}"/>
+    <cellStyle name="Millares 6 3 4 2 2" xfId="4366" xr:uid="{7AF3182D-CAE3-4B2C-B762-54B5DEC34AE3}"/>
     <cellStyle name="Millares 6 3 4 3" xfId="1675" xr:uid="{8173F429-8569-41AF-8DBB-5D4A93BEE44F}"/>
+    <cellStyle name="Millares 6 3 4 3 2" xfId="4367" xr:uid="{1D399738-E409-4161-98A9-A61B042F9417}"/>
+    <cellStyle name="Millares 6 3 4 4" xfId="4365" xr:uid="{27EA18A1-AA10-41EA-B798-E1EB3A5B0D5E}"/>
     <cellStyle name="Millares 6 3 5" xfId="1676" xr:uid="{473DCCAE-8514-4686-984A-911235531C8E}"/>
     <cellStyle name="Millares 6 3 5 2" xfId="1677" xr:uid="{23136BBE-1E13-4A5B-BD79-BCE89D1F8658}"/>
+    <cellStyle name="Millares 6 3 5 2 2" xfId="4369" xr:uid="{3429AFAC-B8F8-4E23-A7C1-424919983232}"/>
     <cellStyle name="Millares 6 3 5 3" xfId="1678" xr:uid="{79AEB125-ECAD-4235-985A-9B64271B15BA}"/>
+    <cellStyle name="Millares 6 3 5 3 2" xfId="4370" xr:uid="{79158327-2837-4512-8A0E-53ABF41795DD}"/>
+    <cellStyle name="Millares 6 3 5 4" xfId="4368" xr:uid="{F515FB61-118E-4C08-BA7B-CECBF22B0AC5}"/>
     <cellStyle name="Millares 6 3 6" xfId="1679" xr:uid="{31112B3A-D620-407C-A583-3551726E2A99}"/>
+    <cellStyle name="Millares 6 3 6 2" xfId="4371" xr:uid="{0299699D-4B82-4A86-950E-4E0382A06A74}"/>
     <cellStyle name="Millares 6 3 7" xfId="1680" xr:uid="{87191360-E33E-490F-8569-B57F47781B7D}"/>
+    <cellStyle name="Millares 6 3 7 2" xfId="4372" xr:uid="{A5D1AC69-0A65-4B90-86B8-B006D37651E1}"/>
     <cellStyle name="Millares 6 3 8" xfId="1681" xr:uid="{64ACB240-52C0-4C59-968C-625CA8390D98}"/>
+    <cellStyle name="Millares 6 3 8 2" xfId="4373" xr:uid="{D7CADF2C-E1A6-40B3-B66A-0C07C1ECCB61}"/>
+    <cellStyle name="Millares 6 3 9" xfId="4361" xr:uid="{6815A294-9AE4-426C-BE88-801D29F9DC01}"/>
     <cellStyle name="Millares 6 4" xfId="1682" xr:uid="{FB807C92-82D5-41FA-BEF4-FA5661ED9A31}"/>
     <cellStyle name="Millares 60" xfId="1683" xr:uid="{4F276396-B0A5-4CFA-B975-B8B9A4A87AAA}"/>
     <cellStyle name="Millares 61" xfId="1684" xr:uid="{9528304A-DC05-4EC5-A476-18B39EE99E0A}"/>
@@ -9002,8 +9577,12 @@
     <cellStyle name="Millares 64" xfId="1687" xr:uid="{A3E5EB82-CADA-494E-80A2-E0B23F8B78CE}"/>
     <cellStyle name="Millares 65" xfId="1688" xr:uid="{0809B6CE-B34D-4E27-BC15-0357004CF0F7}"/>
     <cellStyle name="Millares 65 2" xfId="1689" xr:uid="{988744AC-EBB0-4AD9-9424-4DF6403FBDDF}"/>
+    <cellStyle name="Millares 65 2 2" xfId="4375" xr:uid="{15AAB6B1-5D79-4AD8-A4D4-D7B46D798636}"/>
+    <cellStyle name="Millares 65 3" xfId="4374" xr:uid="{F1B4434E-364E-40F4-B028-761D58202765}"/>
     <cellStyle name="Millares 66" xfId="1690" xr:uid="{1B5EEDCF-FA0E-4A88-A90C-BABA0229DD7A}"/>
     <cellStyle name="Millares 66 2" xfId="1691" xr:uid="{18C92148-91CB-46B2-904C-FB46D070D470}"/>
+    <cellStyle name="Millares 66 2 2" xfId="4377" xr:uid="{12167A85-6EC7-471C-8775-7EF6DE3DF5E7}"/>
+    <cellStyle name="Millares 66 3" xfId="4376" xr:uid="{C4E2ADF7-36EB-4A34-84BE-A8770A95918B}"/>
     <cellStyle name="Millares 67" xfId="1692" xr:uid="{9E646735-91DE-4973-A01A-E8D016FA30AE}"/>
     <cellStyle name="Millares 67 2" xfId="1693" xr:uid="{2C7B14E0-816A-4275-8099-EFC3AC6978DF}"/>
     <cellStyle name="Millares 68" xfId="1694" xr:uid="{49DCCCFF-857B-471F-80CA-23BC17F298EF}"/>
@@ -9014,90 +9593,149 @@
     <cellStyle name="Millares 7 2" xfId="1699" xr:uid="{774FC41F-061B-4268-BB7D-A97F1EA9E876}"/>
     <cellStyle name="Millares 7 2 2" xfId="1700" xr:uid="{64EEE998-CD0D-4F08-A750-CE0404D48AC2}"/>
     <cellStyle name="Millares 7 2 2 2" xfId="1701" xr:uid="{7228568F-3425-4D69-905B-D7E0A98D391D}"/>
+    <cellStyle name="Millares 7 2 2 2 2" xfId="4379" xr:uid="{3C0C9AB6-DF71-404B-AF46-16CA6EC80FF4}"/>
     <cellStyle name="Millares 7 2 2 3" xfId="1702" xr:uid="{D5373810-E852-4520-9364-088523CDA695}"/>
     <cellStyle name="Millares 7 2 2 3 2" xfId="1703" xr:uid="{B7D2ED77-B0E5-46F7-B584-44A82B384394}"/>
+    <cellStyle name="Millares 7 2 2 3 2 2" xfId="4381" xr:uid="{B34447D9-C434-42D2-8449-29E2F1C24CBB}"/>
+    <cellStyle name="Millares 7 2 2 3 3" xfId="4380" xr:uid="{CFEC0C0F-0FA5-4B9F-AE9C-5B9413DD18BC}"/>
     <cellStyle name="Millares 7 2 2 4" xfId="1704" xr:uid="{05557897-4B9B-4E87-B073-FF58BC879D71}"/>
     <cellStyle name="Millares 7 2 2 4 2" xfId="1705" xr:uid="{04901824-EF7A-4F65-B595-1BFF98508F80}"/>
+    <cellStyle name="Millares 7 2 2 4 2 2" xfId="4383" xr:uid="{DA8E0D3B-DF64-4AE9-913C-3DBE07D85690}"/>
     <cellStyle name="Millares 7 2 2 4 3" xfId="1706" xr:uid="{87282E63-D111-4594-A8B7-CD95332FA7C1}"/>
+    <cellStyle name="Millares 7 2 2 4 3 2" xfId="4384" xr:uid="{24EF6214-4300-443C-85AA-1BA57A2F7E51}"/>
+    <cellStyle name="Millares 7 2 2 4 4" xfId="4382" xr:uid="{42878C88-F6A5-4145-9092-1D5DA9418F0F}"/>
     <cellStyle name="Millares 7 2 2 5" xfId="1707" xr:uid="{B4734FF1-57FD-4FBE-BF01-C47B6A656CA9}"/>
     <cellStyle name="Millares 7 2 2 5 2" xfId="1708" xr:uid="{D0EE5BE6-E10A-4FAF-BA7C-4649EA83F85A}"/>
+    <cellStyle name="Millares 7 2 2 5 2 2" xfId="4386" xr:uid="{A99AA7D2-F818-47D4-A9B4-367AF487F001}"/>
     <cellStyle name="Millares 7 2 2 5 3" xfId="1709" xr:uid="{1CFB71F2-0752-4673-AE43-F19416A32D47}"/>
+    <cellStyle name="Millares 7 2 2 5 3 2" xfId="4387" xr:uid="{543F9E4B-7D04-48DF-849E-60AC351B41E2}"/>
+    <cellStyle name="Millares 7 2 2 5 4" xfId="4385" xr:uid="{DCB0F48E-DA74-4E88-BED5-37EA80B53B51}"/>
     <cellStyle name="Millares 7 2 2 6" xfId="1710" xr:uid="{CF39BA93-FC02-49E0-AC23-DD22076D5177}"/>
+    <cellStyle name="Millares 7 2 2 6 2" xfId="4388" xr:uid="{8F54C3C4-F2ED-4E6E-96B1-5C04925CD3E3}"/>
+    <cellStyle name="Millares 7 2 2 7" xfId="4378" xr:uid="{8C9547DE-4A6B-4266-AAB5-8CD1FF15840E}"/>
     <cellStyle name="Millares 7 2 3" xfId="1711" xr:uid="{665262F5-CFF7-47E5-A7DD-828137910080}"/>
     <cellStyle name="Millares 7 2 3 2" xfId="1712" xr:uid="{9C972930-D9C5-4833-B32E-90B7C7E44D2A}"/>
+    <cellStyle name="Millares 7 2 3 2 2" xfId="4389" xr:uid="{F1CAC382-EA4A-4983-AE5D-A8328A8E7C05}"/>
     <cellStyle name="Millares 7 2 4" xfId="1713" xr:uid="{53C038EE-BF06-4EA2-BBE4-861383B94FA2}"/>
     <cellStyle name="Millares 7 2 4 2" xfId="1714" xr:uid="{0225CC20-E81A-4C4D-BAB1-55463D0ACDC1}"/>
+    <cellStyle name="Millares 7 2 4 2 2" xfId="4390" xr:uid="{83C06D36-A651-4955-80F4-6E828848E0DA}"/>
     <cellStyle name="Millares 7 2 4 3" xfId="1715" xr:uid="{7296B067-C8AB-4EAB-8B15-88B500D2BEEB}"/>
     <cellStyle name="Millares 7 2 5" xfId="1716" xr:uid="{8A585151-A583-40AF-B80F-88FF358E4889}"/>
     <cellStyle name="Millares 7 2 5 2" xfId="1717" xr:uid="{63A92CA7-42EE-41A3-805A-5C513B14BD5D}"/>
+    <cellStyle name="Millares 7 2 5 2 2" xfId="4391" xr:uid="{00CBD581-F754-41BA-A79F-C0FE7FFF2EDD}"/>
     <cellStyle name="Millares 7 2 5 3" xfId="1718" xr:uid="{C5A15626-98A1-49AB-9105-95F0014FB533}"/>
     <cellStyle name="Millares 7 2 5 4" xfId="1719" xr:uid="{FFFE3F8B-9EAE-4B1B-B071-3638907DEF4F}"/>
     <cellStyle name="Millares 7 2 6" xfId="1720" xr:uid="{836183EE-C0DF-4ACA-AD9B-8BB41DA8669A}"/>
     <cellStyle name="Millares 7 2 6 2" xfId="1721" xr:uid="{05504E22-A059-4EA8-8774-1F8E630A3701}"/>
+    <cellStyle name="Millares 7 2 6 2 2" xfId="4392" xr:uid="{25E41AEE-B02D-43AF-8B07-EFAECA541F13}"/>
     <cellStyle name="Millares 7 2 6 3" xfId="1722" xr:uid="{FC0D5D10-7AF8-4AFB-9AAF-C79D928ECE3A}"/>
     <cellStyle name="Millares 7 2 6 4" xfId="1723" xr:uid="{A42A33F6-A4DA-45B3-B8A0-AE0FD030F415}"/>
     <cellStyle name="Millares 7 2 7" xfId="1724" xr:uid="{2824069D-6242-4868-A70E-AA919976586E}"/>
+    <cellStyle name="Millares 7 2 7 2" xfId="4393" xr:uid="{5434D701-5F37-4BE9-B064-19FF5F6039FF}"/>
     <cellStyle name="Millares 7 2 8" xfId="1725" xr:uid="{E0265A18-4B82-4F30-9685-DBFD1AE1F943}"/>
+    <cellStyle name="Millares 7 2 8 2" xfId="4394" xr:uid="{ED11AE23-8C75-4AD9-866A-BA22F8FFB3CF}"/>
     <cellStyle name="Millares 7 2 9" xfId="1726" xr:uid="{D3F73DE7-3E2C-46DF-BC5A-48BEC079A666}"/>
     <cellStyle name="Millares 7 3" xfId="1727" xr:uid="{C8F22B7B-86F0-40B3-B8ED-7DBE0DEA1091}"/>
     <cellStyle name="Millares 7 3 2" xfId="1728" xr:uid="{4B2772E0-3446-4989-909D-366FF27606A8}"/>
     <cellStyle name="Millares 7 3 2 2" xfId="1729" xr:uid="{D82BB615-E0B9-4839-9527-709C5981FA68}"/>
+    <cellStyle name="Millares 7 3 2 2 2" xfId="4397" xr:uid="{03D03D20-3EE4-417D-8D75-DDF28637E2D8}"/>
     <cellStyle name="Millares 7 3 2 3" xfId="1730" xr:uid="{624BF114-1DAB-493C-8FEE-7AD1198C83DE}"/>
     <cellStyle name="Millares 7 3 2 3 2" xfId="1731" xr:uid="{AB7EF3DF-A918-4E74-AB0D-5FD9134753A5}"/>
+    <cellStyle name="Millares 7 3 2 3 2 2" xfId="4399" xr:uid="{F6C45BFB-AE9E-48D3-96B0-25AB7426A7E9}"/>
+    <cellStyle name="Millares 7 3 2 3 3" xfId="4398" xr:uid="{DFFD3037-7D74-4247-A4FD-77D6E1EDA798}"/>
     <cellStyle name="Millares 7 3 2 4" xfId="1732" xr:uid="{98B2EAB5-61F0-4FD9-9FFB-4E5940D4FC3C}"/>
     <cellStyle name="Millares 7 3 2 4 2" xfId="1733" xr:uid="{1991F6DB-7862-4A94-967C-C791BB44F64B}"/>
+    <cellStyle name="Millares 7 3 2 4 2 2" xfId="4401" xr:uid="{D1F2DD0E-A60D-49BB-A88B-7895561EFE87}"/>
     <cellStyle name="Millares 7 3 2 4 3" xfId="1734" xr:uid="{EB5093E8-0A24-443E-A6A7-E2AD1B69CB32}"/>
+    <cellStyle name="Millares 7 3 2 4 3 2" xfId="4402" xr:uid="{538D6EB1-0BD1-4D79-905C-1C2DA3E60B70}"/>
+    <cellStyle name="Millares 7 3 2 4 4" xfId="4400" xr:uid="{31954D4D-5ADC-4CA1-82F3-703F15376E70}"/>
     <cellStyle name="Millares 7 3 2 5" xfId="1735" xr:uid="{CAA416FE-276A-4CB9-B73E-2804CADCAD31}"/>
     <cellStyle name="Millares 7 3 2 5 2" xfId="1736" xr:uid="{FB426A45-3883-46CE-89CB-CA581CA73AAF}"/>
+    <cellStyle name="Millares 7 3 2 5 2 2" xfId="4404" xr:uid="{C7CF7310-89E3-4029-8176-AF52D51FDAF9}"/>
     <cellStyle name="Millares 7 3 2 5 3" xfId="1737" xr:uid="{2AB63D6D-4147-44E7-94B7-4E1F33AB1E85}"/>
+    <cellStyle name="Millares 7 3 2 5 3 2" xfId="4405" xr:uid="{302495FC-603A-4DE5-9289-7CD8BD749B78}"/>
+    <cellStyle name="Millares 7 3 2 5 4" xfId="4403" xr:uid="{E65A6871-4A09-4F23-95E0-76384354936F}"/>
     <cellStyle name="Millares 7 3 2 6" xfId="1738" xr:uid="{1176DBE4-C1F1-41AB-8591-0215884E110A}"/>
+    <cellStyle name="Millares 7 3 2 6 2" xfId="4406" xr:uid="{80EE7F4F-A35B-4752-AAC4-54AA4D1133BE}"/>
+    <cellStyle name="Millares 7 3 2 7" xfId="4396" xr:uid="{31243AF3-8AAE-47CD-AEDC-2EA7D3536DD7}"/>
     <cellStyle name="Millares 7 3 3" xfId="1739" xr:uid="{DB74D178-916F-4046-9012-91113B3C04BB}"/>
+    <cellStyle name="Millares 7 3 3 2" xfId="4407" xr:uid="{C26B581C-D85E-434E-A98F-52979915E67C}"/>
     <cellStyle name="Millares 7 3 4" xfId="1740" xr:uid="{F80CB61D-AA9C-4021-9B2C-C47E7AA6D93B}"/>
+    <cellStyle name="Millares 7 3 4 2" xfId="4408" xr:uid="{EFD75FEF-344D-42D0-8BE3-2F257FC9548F}"/>
     <cellStyle name="Millares 7 3 5" xfId="1741" xr:uid="{464092A4-5176-49A7-A658-F30D68552C27}"/>
+    <cellStyle name="Millares 7 3 5 2" xfId="4409" xr:uid="{0E93AEEE-3DF6-4C18-B923-4FC13775F82C}"/>
     <cellStyle name="Millares 7 3 6" xfId="1742" xr:uid="{49434636-D202-481A-BAB6-D795DDA3B2FC}"/>
+    <cellStyle name="Millares 7 3 6 2" xfId="4410" xr:uid="{EF821DEA-96D8-4AB9-B7C5-3754A8B506FC}"/>
     <cellStyle name="Millares 7 3 7" xfId="1743" xr:uid="{F9D19529-41A5-4AE6-8015-FEAC9061E1F0}"/>
+    <cellStyle name="Millares 7 3 7 2" xfId="4411" xr:uid="{0254E8EA-CC97-4755-8D8E-5AB0D755F28C}"/>
     <cellStyle name="Millares 7 3 8" xfId="1744" xr:uid="{D054169B-02E8-4BF1-9DD2-5EB4488FE08D}"/>
+    <cellStyle name="Millares 7 3 8 2" xfId="4412" xr:uid="{E3202A77-BBEE-4797-AE54-C12C56B1A6E3}"/>
+    <cellStyle name="Millares 7 3 9" xfId="4395" xr:uid="{32C22C9D-92CC-42D4-9084-B93703E8CB38}"/>
     <cellStyle name="Millares 7 4" xfId="1745" xr:uid="{9438CE45-D1BF-4A91-AF4C-87403D7F3159}"/>
     <cellStyle name="Millares 70" xfId="1746" xr:uid="{3BEF2378-BD3A-4A04-8096-605CFFA6699B}"/>
     <cellStyle name="Millares 70 2" xfId="1747" xr:uid="{E68E7EC9-A29F-4E9C-9C7B-68928BF3E9F3}"/>
     <cellStyle name="Millares 71" xfId="1748" xr:uid="{839D2071-BDAA-4A10-BCDF-2ECEE2A31A62}"/>
     <cellStyle name="Millares 71 2" xfId="1749" xr:uid="{A99D5E2E-199C-4B9B-A69C-1DB5B0744A00}"/>
+    <cellStyle name="Millares 71 2 2" xfId="4414" xr:uid="{CB583CB3-7FA5-4981-99E5-58A4C22E8A40}"/>
+    <cellStyle name="Millares 71 3" xfId="4413" xr:uid="{7877857A-F708-49E3-9258-784BD8D1715B}"/>
     <cellStyle name="Millares 72" xfId="1750" xr:uid="{8D9EED0F-0F4F-4DEA-9C43-1E6DA675E4FC}"/>
     <cellStyle name="Millares 72 2" xfId="1751" xr:uid="{C8F12155-2638-4D18-87EF-6F84A69F2CC7}"/>
+    <cellStyle name="Millares 72 2 2" xfId="4416" xr:uid="{A5F644BC-FCF2-4D07-A541-F1CF3F198867}"/>
+    <cellStyle name="Millares 72 3" xfId="4415" xr:uid="{1A85EEBF-D7F6-47D2-8A15-27CA2FEA726A}"/>
     <cellStyle name="Millares 73" xfId="1752" xr:uid="{8E063B87-9ACF-493B-B3C5-D1ECA77E9875}"/>
     <cellStyle name="Millares 73 2" xfId="1753" xr:uid="{9759B43D-4348-4D9E-8E7B-75ED30334B50}"/>
+    <cellStyle name="Millares 73 3" xfId="4417" xr:uid="{4FAF7FA3-8721-443D-98C8-D32209FD93D9}"/>
     <cellStyle name="Millares 74" xfId="1754" xr:uid="{9E0B67B0-F025-4129-95F5-C5B7577FC545}"/>
     <cellStyle name="Millares 74 2" xfId="1755" xr:uid="{7E0D9A98-470D-4C65-8089-AAC9D8DCF755}"/>
+    <cellStyle name="Millares 74 3" xfId="4418" xr:uid="{8BFFE5BB-4792-45B2-9056-7105B75E2308}"/>
     <cellStyle name="Millares 75" xfId="1756" xr:uid="{9B493AB1-95F5-4AD1-BE44-969EF289138C}"/>
     <cellStyle name="Millares 75 2" xfId="1757" xr:uid="{50DD0665-0F24-4388-BC66-4AABEF50D80F}"/>
     <cellStyle name="Millares 75 3" xfId="1758" xr:uid="{EC9CD845-3E62-4E23-B7C2-0A04C1011822}"/>
+    <cellStyle name="Millares 75 4" xfId="4419" xr:uid="{6E1F23FE-E8D1-493E-B199-D9E0E80C647F}"/>
     <cellStyle name="Millares 76" xfId="1759" xr:uid="{E2A33FE2-136C-4C3A-9B16-6628DBD4F09A}"/>
     <cellStyle name="Millares 77" xfId="1760" xr:uid="{49C78967-5E1D-4053-A6B7-DE903539D810}"/>
+    <cellStyle name="Millares 77 2" xfId="4420" xr:uid="{B1BBD9F4-714A-46FD-81EF-71EB406D1208}"/>
     <cellStyle name="Millares 78" xfId="1761" xr:uid="{BA87C0AE-8C8A-43A6-82D7-0919BA311F6A}"/>
+    <cellStyle name="Millares 78 2" xfId="4421" xr:uid="{F53D0FF6-260D-433C-983B-4201965091A5}"/>
     <cellStyle name="Millares 79" xfId="1762" xr:uid="{9F78FBBC-7027-4FFD-9FD3-B9865B0AC370}"/>
+    <cellStyle name="Millares 79 2" xfId="4422" xr:uid="{01A66C2F-8463-4B0D-917E-FE2BB2242552}"/>
     <cellStyle name="Millares 8" xfId="1763" xr:uid="{DAF83C15-138F-4F95-B647-C31D6479FC2E}"/>
     <cellStyle name="Millares 8 2" xfId="1764" xr:uid="{1CFFA06C-F657-41F3-9915-675B88F70C50}"/>
+    <cellStyle name="Millares 8 2 2" xfId="4424" xr:uid="{D9AD15FA-0D92-4434-858C-A3EF6A88A896}"/>
     <cellStyle name="Millares 8 3" xfId="1765" xr:uid="{DEB26FC6-26CD-4C6B-98F7-E64766B94338}"/>
+    <cellStyle name="Millares 8 4" xfId="4423" xr:uid="{7D30DBDC-AF86-4B15-905F-A72FDA182806}"/>
     <cellStyle name="Millares 80" xfId="1766" xr:uid="{F3DBD995-78B7-47CB-A596-473F9EB24804}"/>
+    <cellStyle name="Millares 80 2" xfId="4425" xr:uid="{46814F5E-DBFF-4B8E-9A78-20CD02A9ED10}"/>
     <cellStyle name="Millares 81" xfId="1767" xr:uid="{B7F355D7-2401-4DF7-8B83-1F1C7F1B0C12}"/>
+    <cellStyle name="Millares 81 2" xfId="4426" xr:uid="{BCE4AA6A-50E9-4D8A-B4BB-11F73F35E16E}"/>
     <cellStyle name="Millares 82" xfId="1768" xr:uid="{48B95C98-3E61-435A-98A9-FC8246BFF06D}"/>
+    <cellStyle name="Millares 82 2" xfId="4427" xr:uid="{D74C6A6C-4D6D-4CD8-B469-9D4E66CA7415}"/>
     <cellStyle name="Millares 83" xfId="1769" xr:uid="{114AB59C-3770-4833-BD77-91008E5125DD}"/>
+    <cellStyle name="Millares 83 2" xfId="4428" xr:uid="{F960CFAA-9C42-4E7B-A138-2D75E7185CCD}"/>
     <cellStyle name="Millares 84" xfId="1770" xr:uid="{52BD16C4-79F4-4264-93C3-0C5414BE215C}"/>
     <cellStyle name="Millares 85" xfId="1771" xr:uid="{7E448134-B81C-4C63-8420-CB939E0F6EA1}"/>
     <cellStyle name="Millares 86" xfId="1772" xr:uid="{7074A2C6-4025-41B4-9840-FADB118AA9FB}"/>
     <cellStyle name="Millares 87" xfId="1773" xr:uid="{363415BA-DE35-4948-AF39-A7E694EA7F1D}"/>
+    <cellStyle name="Millares 87 2" xfId="4429" xr:uid="{A2C72B46-8ED2-414F-A75C-463039A000BF}"/>
     <cellStyle name="Millares 88" xfId="1774" xr:uid="{763A6865-610F-44CA-A51A-1BD7491D5BD0}"/>
+    <cellStyle name="Millares 88 2" xfId="4430" xr:uid="{166EBD2A-AD02-40D7-B819-FAD937DD4ECF}"/>
     <cellStyle name="Millares 89" xfId="1775" xr:uid="{3F7E371C-CD7C-4DAC-9D89-A3C831232288}"/>
+    <cellStyle name="Millares 89 2" xfId="4431" xr:uid="{C371C179-BB87-4DEC-AE22-4CC745F62249}"/>
     <cellStyle name="Millares 9" xfId="1776" xr:uid="{F2A06B86-BE6C-43D7-AC0E-79058C8344F2}"/>
     <cellStyle name="Millares 9 11" xfId="1777" xr:uid="{9D965B6F-F4F3-4714-90EE-EA556F7FC964}"/>
     <cellStyle name="Millares 9 2" xfId="1778" xr:uid="{F0DB686F-9091-477F-A7DD-6B4E9755DB6D}"/>
     <cellStyle name="Millares 90" xfId="1779" xr:uid="{82B5941C-3FD6-4A04-AACD-24A6E1B83746}"/>
     <cellStyle name="Millares 91" xfId="1780" xr:uid="{AB809D24-D52D-4CAB-9337-9B104E2665DC}"/>
     <cellStyle name="Millares 92" xfId="1781" xr:uid="{8365789C-48B1-42F2-A5FA-395D7EBD8B2D}"/>
+    <cellStyle name="Millares 92 2" xfId="4432" xr:uid="{0BF9FAB1-F4BB-4FAC-B4BE-4210026E777D}"/>
     <cellStyle name="Millares 93" xfId="1782" xr:uid="{350E8161-3EA3-4464-A688-D6C9A5348206}"/>
+    <cellStyle name="Millares 93 2" xfId="4433" xr:uid="{4E270C38-5713-4344-AA5C-490532BC5EE2}"/>
     <cellStyle name="Millares 94" xfId="1783" xr:uid="{49B6624C-1B76-4ED0-B978-0AE854F5BF40}"/>
+    <cellStyle name="Millares 94 2" xfId="4434" xr:uid="{E10BA584-6553-497C-BEED-35E8EAEFE0B5}"/>
     <cellStyle name="Millares 95" xfId="1784" xr:uid="{49EAA12A-F2BF-4F3D-B203-A68A1B1711C0}"/>
+    <cellStyle name="Millares 95 2" xfId="4435" xr:uid="{26AB93ED-874C-4022-8BA2-BA474D144298}"/>
     <cellStyle name="Millares 96" xfId="1785" xr:uid="{A5939491-2EE7-4D7E-B527-DA763C0508F6}"/>
+    <cellStyle name="Millares 96 2" xfId="4436" xr:uid="{D6052F79-5E25-4FC9-B3F4-073F6C2BA672}"/>
     <cellStyle name="Moneda 2" xfId="1786" xr:uid="{8E603F92-B619-4330-B7BE-80B19A4D0A3F}"/>
     <cellStyle name="Moneda 2 2" xfId="1787" xr:uid="{D713E94B-33C1-4023-928C-48F3DF370644}"/>
     <cellStyle name="Moneda 3" xfId="1788" xr:uid="{AC518FE8-9FA1-4199-BD85-2512FF88C3EA}"/>
@@ -15890,10 +16528,10 @@
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="2:23">
@@ -15965,7 +16603,7 @@
         <v>17</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W5" s="3" t="s">
         <v>11</v>
@@ -15973,31 +16611,20 @@
     </row>
     <row r="6" spans="2:23" ht="45">
       <c r="B6" s="19" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="19">
-        <v>2023</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="38">
-        <v>0.8</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>167</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="19"/>
       <c r="N6" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>193</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>194</v>
       </c>
       <c r="R6" s="19">
         <v>2023</v>
@@ -16015,12 +16642,12 @@
         <v>5</v>
       </c>
       <c r="W6" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="2:23">
       <c r="B7" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>146</v>
@@ -16217,12 +16844,12 @@
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J18" s="39"/>
       <c r="K18" s="39"/>
       <c r="L18" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -16245,7 +16872,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L19" s="17" t="s">
         <v>116</v>
@@ -16271,7 +16898,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -16346,10 +16973,10 @@
         <v>1.5</v>
       </c>
       <c r="I25" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="40" t="s">
         <v>172</v>
-      </c>
-      <c r="L25" s="40" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -16372,10 +16999,10 @@
         <v>13.8</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L26" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -16398,10 +17025,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="L27" s="40" t="s">
         <v>175</v>
-      </c>
-      <c r="L27" s="40" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -16424,7 +17051,7 @@
         <v>5</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -16448,7 +17075,7 @@
       </c>
       <c r="H29" s="39"/>
       <c r="I29" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -16472,7 +17099,7 @@
       </c>
       <c r="H30" s="39"/>
       <c r="I30" s="39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -16496,10 +17123,10 @@
       </c>
       <c r="H31" s="39"/>
       <c r="I31" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="L31" s="40" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -16523,10 +17150,10 @@
       </c>
       <c r="H32" s="39"/>
       <c r="I32" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="L32" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="L32" s="40" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -16550,7 +17177,7 @@
       </c>
       <c r="H33" s="39"/>
       <c r="I33" s="39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -16781,7 +17408,7 @@
         <v>0.2</v>
       </c>
       <c r="J50" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="2:10">
@@ -16804,7 +17431,7 @@
         <v>1.5</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="2:10">
@@ -16827,7 +17454,7 @@
         <v>3</v>
       </c>
       <c r="J52" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="2:10">
@@ -16850,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="J53" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="2:10">
@@ -16873,7 +17500,7 @@
         <v>8</v>
       </c>
       <c r="J54" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:10">
@@ -16898,7 +17525,7 @@
         <v>10</v>
       </c>
       <c r="J55" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -16986,7 +17613,7 @@
         <v>166</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -17072,6 +17699,138 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC00144-1DB4-462F-B9FF-FF65841ABAD9}">
+  <dimension ref="C5:L10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="5" spans="3:12">
+      <c r="C5" s="92" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+    </row>
+    <row r="6" spans="3:12">
+      <c r="C6" s="92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+    </row>
+    <row r="7" spans="3:12">
+      <c r="C7" s="91"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+    </row>
+    <row r="8" spans="3:12">
+      <c r="C8" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="93" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="93" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="95" t="s">
+        <v>255</v>
+      </c>
+      <c r="K8" s="95" t="s">
+        <v>256</v>
+      </c>
+      <c r="L8" s="94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" ht="30">
+      <c r="C9" s="96" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="91"/>
+      <c r="E9" s="97" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="96" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="96">
+        <v>2025</v>
+      </c>
+      <c r="H9" s="96" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="91">
+        <v>0.41</v>
+      </c>
+      <c r="J9" s="98">
+        <v>0</v>
+      </c>
+      <c r="K9" s="91">
+        <v>5</v>
+      </c>
+      <c r="L9" s="96" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12">
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91" t="s">
+        <v>264</v>
+      </c>
+      <c r="F10" s="91" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91">
+        <v>-0.59000000000000008</v>
+      </c>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:V60"/>
@@ -17182,7 +17941,7 @@
       </c>
       <c r="C6" s="39"/>
       <c r="D6" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
@@ -17199,7 +17958,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M6" s="19" t="s">
         <v>111</v>
@@ -17514,7 +18273,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="H16" t="s">
-        <v>7</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -17943,18 +18702,18 @@
     </row>
     <row r="53" spans="2:11">
       <c r="E53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="2:11" ht="15.75" thickBot="1">
       <c r="B54" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C54" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="C54" s="52" t="s">
+      <c r="D54" s="52" t="s">
         <v>182</v>
-      </c>
-      <c r="D54" s="52" t="s">
-        <v>183</v>
       </c>
       <c r="E54" s="52">
         <v>2020</v>
@@ -17980,7 +18739,7 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C55" s="19">
         <v>34.700000000000003</v>
@@ -18012,7 +18771,7 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C56" s="19">
         <v>34.700000000000003</v>
@@ -18044,7 +18803,7 @@
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C57" s="19">
         <v>36.6</v>
@@ -18076,7 +18835,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C58" s="44">
         <v>40.299999999999997</v>
@@ -18109,7 +18868,7 @@
     <row r="59" spans="2:11">
       <c r="C59" s="47"/>
       <c r="D59" s="47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E59" s="47">
         <v>1.8</v>
@@ -18135,10 +18894,10 @@
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="51" t="s">
         <v>189</v>
-      </c>
-      <c r="C60" s="51" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -18146,7 +18905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F532AC2E-E047-4124-A56C-AD8CA9B97A1E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:I12"/>
@@ -18364,7 +19123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FB1178-AF9A-473D-9FB3-41C2F896D89C}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B3:M91"/>
@@ -18429,7 +19188,7 @@
         <v>104</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I5" s="86" t="str">
         <f>H5</f>
@@ -18470,13 +19229,13 @@
         <v>0</v>
       </c>
       <c r="C14" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D14" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="77" t="s">
         <v>2</v>
@@ -18485,39 +19244,39 @@
         <v>9</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I14" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J14" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K14" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F15" s="19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>164</v>
@@ -18533,7 +19292,7 @@
         <v>5</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -18545,10 +19304,10 @@
     <row r="16" spans="2:13">
       <c r="B16" s="19"/>
       <c r="D16" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F16" s="19">
         <v>2030</v>
@@ -18569,10 +19328,10 @@
     <row r="17" spans="2:13">
       <c r="B17" s="19"/>
       <c r="D17" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F17" s="19">
         <v>2051</v>
@@ -18591,19 +19350,19 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F18" s="19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G18" s="19" t="s">
         <v>81</v>
@@ -18619,7 +19378,7 @@
         <v>5</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -18631,10 +19390,10 @@
     <row r="19" spans="2:13">
       <c r="B19" s="19"/>
       <c r="D19" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F19" s="19">
         <v>2030</v>
@@ -18656,10 +19415,10 @@
       <c r="B20" s="44"/>
       <c r="C20" s="18"/>
       <c r="D20" s="81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F20" s="44">
         <v>2050</v>
@@ -18711,13 +19470,13 @@
         <v>0</v>
       </c>
       <c r="C26" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D26" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F26" s="77" t="s">
         <v>2</v>
@@ -18726,39 +19485,39 @@
         <v>9</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I26" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J26" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K26" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F27" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G27" s="19" t="s">
         <v>164</v>
@@ -18774,7 +19533,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -18786,10 +19545,10 @@
     <row r="28" spans="2:13">
       <c r="B28" s="19"/>
       <c r="D28" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F28" s="19">
         <v>2040</v>
@@ -18808,10 +19567,10 @@
     <row r="29" spans="2:13">
       <c r="B29" s="19"/>
       <c r="D29" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F29" s="19">
         <v>2055</v>
@@ -18829,19 +19588,19 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F30" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G30" s="19" t="s">
         <v>81</v>
@@ -18857,7 +19616,7 @@
         <v>5</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -18870,10 +19629,10 @@
       <c r="B31" s="44"/>
       <c r="C31" s="18"/>
       <c r="D31" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F31" s="44">
         <v>2040</v>
@@ -18893,10 +19652,10 @@
     </row>
     <row r="32" spans="2:13">
       <c r="D32" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F32" s="44">
         <v>2050</v>
@@ -18943,13 +19702,13 @@
         <v>0</v>
       </c>
       <c r="C38" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D38" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E38" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F38" s="77" t="s">
         <v>2</v>
@@ -18958,39 +19717,39 @@
         <v>9</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I38" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J38" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K38" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F39" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G39" s="19" t="s">
         <v>164</v>
@@ -19006,7 +19765,7 @@
         <v>5</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -19018,10 +19777,10 @@
     <row r="40" spans="2:13">
       <c r="B40" s="19"/>
       <c r="D40" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F40" s="19">
         <v>2040</v>
@@ -19041,10 +19800,10 @@
     <row r="41" spans="2:13">
       <c r="B41" s="19"/>
       <c r="D41" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F41" s="19">
         <v>2055</v>
@@ -19063,19 +19822,19 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F42" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G42" s="19" t="s">
         <v>81</v>
@@ -19091,7 +19850,7 @@
         <v>5</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -19104,10 +19863,10 @@
       <c r="B43" s="44"/>
       <c r="C43" s="18"/>
       <c r="D43" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F43" s="44">
         <v>2040</v>
@@ -19127,10 +19886,10 @@
     </row>
     <row r="44" spans="2:13">
       <c r="D44" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F44" s="44">
         <v>2050</v>
@@ -19182,13 +19941,13 @@
         <v>0</v>
       </c>
       <c r="C50" s="77" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D50" s="77" t="s">
         <v>3</v>
       </c>
       <c r="E50" s="77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F50" s="77" t="s">
         <v>2</v>
@@ -19197,39 +19956,39 @@
         <v>9</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I50" s="78" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J50" s="78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K50" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F51" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G51" s="19" t="s">
         <v>164</v>
@@ -19245,7 +20004,7 @@
         <v>5</v>
       </c>
       <c r="K51" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -19257,10 +20016,10 @@
     <row r="52" spans="2:13">
       <c r="B52" s="19"/>
       <c r="D52" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F52" s="19">
         <v>2040</v>
@@ -19276,16 +20035,16 @@
       </c>
       <c r="J52" s="19"/>
       <c r="K52" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" spans="2:13">
       <c r="B53" s="19"/>
       <c r="D53" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F53" s="19">
         <v>2051</v>
@@ -19304,19 +20063,19 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F54" s="19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G54" s="19" t="s">
         <v>81</v>
@@ -19332,7 +20091,7 @@
         <v>5</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -19345,10 +20104,10 @@
       <c r="B55" s="44"/>
       <c r="C55" s="18"/>
       <c r="D55" s="81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F55" s="44">
         <v>2040</v>
@@ -19365,15 +20124,15 @@
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="2:13">
       <c r="D56" s="81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F56" s="44">
         <v>2050</v>
@@ -19396,7 +20155,7 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" s="58"/>
       <c r="D60" s="58"/>
@@ -19424,7 +20183,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="59" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C62" s="60">
         <v>121157</v>
@@ -19447,7 +20206,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C63" s="60">
         <v>25459</v>
@@ -19470,7 +20229,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C64" s="60">
         <v>157865</v>
@@ -19493,7 +20252,7 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" s="59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C65" s="63">
         <v>304481</v>
@@ -19516,7 +20275,7 @@
     </row>
     <row r="66" spans="2:8">
       <c r="B66" s="59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C66" s="60">
         <v>99456</v>
@@ -19539,7 +20298,7 @@
     </row>
     <row r="67" spans="2:8">
       <c r="B67" s="59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C67" s="60">
         <v>14859</v>
@@ -19562,7 +20321,7 @@
     </row>
     <row r="68" spans="2:8">
       <c r="B68" s="59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C68" s="60">
         <v>125874</v>
@@ -19585,7 +20344,7 @@
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C69" s="62">
         <v>240189</v>
@@ -19608,17 +20367,17 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" s="59" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15.75">
       <c r="B73" s="59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C73" s="64">
         <v>2018</v>
@@ -19641,7 +20400,7 @@
     </row>
     <row r="74" spans="2:8">
       <c r="B74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C74" s="56">
         <f>C62+C66</f>
@@ -19670,7 +20429,7 @@
     </row>
     <row r="75" spans="2:8">
       <c r="B75" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C75" s="56">
         <f>C63+C67</f>
@@ -19699,7 +20458,7 @@
     </row>
     <row r="76" spans="2:8">
       <c r="B76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" s="56">
         <f>C75*$G$88</f>
@@ -19728,7 +20487,7 @@
     </row>
     <row r="77" spans="2:8">
       <c r="B77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C77" s="56">
         <f>C75*$G$89</f>
@@ -19757,7 +20516,7 @@
     </row>
     <row r="78" spans="2:8">
       <c r="B78" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C78" s="56">
         <f>C75*$G$90</f>
@@ -19786,15 +20545,15 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:8">
       <c r="B83" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C83" s="68" t="s">
         <v>221</v>
-      </c>
-      <c r="C83" s="68" t="s">
-        <v>222</v>
       </c>
       <c r="G83">
         <v>2022</v>
@@ -19805,13 +20564,13 @@
     </row>
     <row r="84" spans="2:8">
       <c r="B84" s="69" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C84" s="70">
         <v>387723</v>
       </c>
       <c r="F84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G84">
         <f>C85+C86</f>
@@ -19823,13 +20582,13 @@
     </row>
     <row r="85" spans="2:8">
       <c r="B85" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="72">
         <v>222953</v>
       </c>
       <c r="F85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G85">
         <f>C87+C88</f>
@@ -19841,13 +20600,13 @@
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="69" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C86" s="70">
         <v>127727</v>
       </c>
       <c r="F86" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G86">
         <f>C89+C90</f>
@@ -19859,24 +20618,24 @@
     </row>
     <row r="87" spans="2:8">
       <c r="B87" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C87" s="72">
         <v>4421</v>
       </c>
       <c r="G87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="2:8">
       <c r="B88" s="69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C88" s="70">
         <v>6802</v>
       </c>
       <c r="F88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G88" s="54">
         <f>G84/$C$84</f>
@@ -19885,13 +20644,13 @@
     </row>
     <row r="89" spans="2:8">
       <c r="B89" s="71" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C89" s="72">
         <v>9100</v>
       </c>
       <c r="F89" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G89" s="54">
         <f t="shared" ref="G89:G90" si="5">G85/$C$84</f>
@@ -19900,13 +20659,13 @@
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C90" s="66">
         <v>16721</v>
       </c>
       <c r="F90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G90" s="54">
         <f t="shared" si="5"/>
@@ -19915,7 +20674,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
+++ b/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A769C7-5DDA-4443-B9A4-54B4D6ADD9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91AF77D-2E8D-44EF-B8A8-7C6724294118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="266">
   <si>
     <t>UC_N</t>
   </si>
@@ -1020,7 +1020,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="32">
+  <numFmts count="30">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
@@ -1051,10 +1051,8 @@
     <numFmt numFmtId="189" formatCode="[$-340A]d&quot; de &quot;mmmm&quot; de &quot;yyyy;@"/>
     <numFmt numFmtId="190" formatCode="0.0%"/>
     <numFmt numFmtId="191" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="193" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="195" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="137">
+  <fonts count="136">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,13 +1174,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2877,7 +2868,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -2889,133 +2880,133 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3025,70 +3016,70 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="122" fillId="44" borderId="0">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="121" fillId="44" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3100,32 +3091,32 @@
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3137,31 +3128,31 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3173,31 +3164,31 @@
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3209,46 +3200,46 @@
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3260,38 +3251,38 @@
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="85" fillId="54" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="84" fillId="54" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3303,47 +3294,47 @@
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3355,31 +3346,31 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3391,48 +3382,48 @@
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3444,699 +3435,699 @@
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="123" fillId="54" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="122" fillId="54" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="90" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="90" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="68" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="68" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="91" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="91" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="87" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="70" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="87" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="90" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="70" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="172" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4153,51 +4144,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="175" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4238,7 +4229,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4246,548 +4237,548 @@
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="2" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="98" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="68" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="97" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="98" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="97" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="99" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="98" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="98" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="190" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="121" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="120" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="191" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4797,90 +4788,90 @@
     <xf numFmtId="183" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="185" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="125" fillId="44" borderId="2">
+    <xf numFmtId="185" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="124" fillId="44" borderId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="126" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="125" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -4901,7 +4892,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4916,43 +4907,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="127" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="78" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="126" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4988,15 +4979,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5039,10 +5030,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5060,9 +5051,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5086,13 +5077,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5115,61 +5106,106 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="135" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="133" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5179,74 +5215,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="134" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5338,146 +5329,146 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5485,9 +5476,9 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5495,16 +5486,16 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5540,328 +5531,328 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="100" fillId="73" borderId="32">
+    <xf numFmtId="0" fontId="19" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="99" fillId="73" borderId="32">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="33">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="33">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="92" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5874,112 +5865,112 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="13" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6000,90 +5991,90 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6104,7 +6095,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6115,34 +6106,34 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6153,189 +6144,189 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6344,671 +6335,671 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="101" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="101" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="123" fillId="74" borderId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="100" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="100" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="122" fillId="74" borderId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="121" fillId="74" borderId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="128" fillId="74" borderId="0">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="127" fillId="74" borderId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="125" fillId="9" borderId="2">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="124" fillId="9" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="132" fillId="74" borderId="0">
+    <xf numFmtId="3" fontId="131" fillId="74" borderId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7071,8 +7062,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7095,7 +7086,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7172,308 +7163,308 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="121" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="120" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7558,7 +7549,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7583,45 +7573,45 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="14" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="45" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="17" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="16" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="17" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="16" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -7656,20 +7646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12910,17 +12886,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79DA532-7D5D-4233-BA89-FC4C950C7D0C}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="10" width="8.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="1" max="4" width="21.7265625" customWidth="1"/>
+    <col min="5" max="6" width="14.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="10" width="8.1796875" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -13344,12 +13320,12 @@
       <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26" ht="102.75" customHeight="1">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="24"/>
@@ -13433,11 +13409,11 @@
       <c r="A19" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
       <c r="G19" s="30"/>
@@ -13465,11 +13441,11 @@
       <c r="A20" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
       <c r="E20" s="29"/>
       <c r="F20" s="29"/>
       <c r="G20" s="30"/>
@@ -13557,11 +13533,11 @@
       <c r="A23" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="88" t="s">
+      <c r="B23" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -13647,11 +13623,11 @@
       <c r="A26" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -13767,11 +13743,11 @@
       <c r="A30" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="90" t="s">
+      <c r="B30" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
       <c r="G30" s="22"/>
@@ -13799,11 +13775,11 @@
       <c r="A31" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="88" t="s">
+      <c r="B31" s="87" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
       <c r="G31" s="22"/>
@@ -15757,36 +15733,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F0F7499-A5CE-4374-995E-DC72D788363A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.54296875" customWidth="1"/>
+    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -16257,7 +16233,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+    <row r="10" spans="1:30" ht="15" thickBot="1">
       <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
@@ -16518,12 +16494,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE79BAD-EA44-47F0-A194-320DE6C9FB50}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:W62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
@@ -16609,7 +16585,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="45">
+    <row r="6" spans="2:23" ht="43.5">
       <c r="B6" s="19" t="s">
         <v>257</v>
       </c>
@@ -16777,7 +16753,7 @@
       </c>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:23" ht="15.75" thickBot="1">
+    <row r="16" spans="2:23" ht="15" thickBot="1">
       <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
@@ -16924,7 +16900,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15.75" thickBot="1">
+    <row r="24" spans="2:12" ht="15" thickBot="1">
       <c r="B24" s="8" t="s">
         <v>12</v>
       </c>
@@ -17007,25 +16983,28 @@
     </row>
     <row r="27" spans="2:12">
       <c r="B27" s="39" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="41">
-        <v>2026</v>
-      </c>
-      <c r="F27" s="39">
-        <v>0</v>
-      </c>
-      <c r="G27" s="39">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="39" t="s">
+        <v>107</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="L27" s="40" t="s">
         <v>175</v>
@@ -17194,7 +17173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="15.75" thickBot="1">
+    <row r="37" spans="2:12" ht="15" thickBot="1">
       <c r="B37" s="8" t="s">
         <v>12</v>
       </c>
@@ -17504,27 +17483,27 @@
       </c>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="44" t="s">
+      <c r="B55" s="43" t="s">
         <v>160</v>
       </c>
       <c r="C55" s="18"/>
-      <c r="D55" s="81" t="s">
+      <c r="D55" s="80" t="s">
         <v>161</v>
       </c>
       <c r="E55" s="18"/>
-      <c r="F55" s="44">
+      <c r="F55" s="43">
         <v>2032</v>
       </c>
-      <c r="G55" s="84" t="s">
+      <c r="G55" s="83" t="s">
         <v>81</v>
       </c>
       <c r="H55" s="18">
         <v>1</v>
       </c>
-      <c r="I55" s="84">
+      <c r="I55" s="83">
         <v>10</v>
       </c>
-      <c r="J55" s="44" t="s">
+      <c r="J55" s="43" t="s">
         <v>167</v>
       </c>
     </row>
@@ -17612,7 +17591,7 @@
       <c r="B62" t="s">
         <v>166</v>
       </c>
-      <c r="J62" s="85" t="s">
+      <c r="J62" s="84" t="s">
         <v>248</v>
       </c>
     </row>
@@ -17631,10 +17610,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE4666E-C19A-4073-8183-3ACBB585B13C}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:J4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
@@ -17645,7 +17624,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1">
+    <row r="3" spans="2:10" ht="15" thickBot="1">
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
@@ -17701,129 +17680,94 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC00144-1DB4-462F-B9FF-FF65841ABAD9}">
   <dimension ref="C5:L10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="5" spans="3:12">
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91" t="s">
+      <c r="H7" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="93" t="s">
+      <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="93" t="s">
+      <c r="G8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="91" t="s">
+      <c r="I8" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="95" t="s">
+      <c r="J8" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="K8" s="95" t="s">
+      <c r="K8" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="L8" s="94" t="s">
+      <c r="L8" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="3:12" ht="30">
-      <c r="C9" s="96" t="s">
+    <row r="9" spans="3:12" ht="29">
+      <c r="C9" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="91"/>
-      <c r="E9" s="97" t="s">
+      <c r="E9" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="96" t="s">
+      <c r="F9" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="19">
         <v>2025</v>
       </c>
-      <c r="H9" s="96" t="s">
+      <c r="H9" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="I9" s="91">
+      <c r="I9">
         <v>0.41</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="38">
         <v>0</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9">
         <v>5</v>
       </c>
-      <c r="L9" s="96" t="s">
+      <c r="L9" s="19" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91" t="s">
+      <c r="E10" t="s">
         <v>264</v>
       </c>
-      <c r="F10" s="91" t="s">
+      <c r="F10" t="s">
         <v>265</v>
       </c>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91">
+      <c r="I10">
         <v>-0.59000000000000008</v>
       </c>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17834,19 +17778,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" customWidth="1"/>
-    <col min="12" max="12" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.26953125" customWidth="1"/>
+    <col min="12" max="12" width="44.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17935,12 +17879,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="30">
+    <row r="6" spans="1:22" ht="29">
       <c r="B6" s="38" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="39"/>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="41" t="s">
         <v>190</v>
       </c>
       <c r="E6" s="39"/>
@@ -17985,7 +17929,7 @@
     <row r="7" spans="1:22">
       <c r="B7" s="38"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="42"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
       <c r="G7" s="38">
@@ -18016,7 +17960,7 @@
         <v>115</v>
       </c>
       <c r="C8" s="39"/>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E8" s="38"/>
@@ -18062,7 +18006,7 @@
     <row r="9" spans="1:22">
       <c r="B9" s="38"/>
       <c r="C9" s="39"/>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="38"/>
@@ -18093,7 +18037,7 @@
     <row r="10" spans="1:22">
       <c r="B10" s="38"/>
       <c r="C10" s="38"/>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E10" s="38"/>
@@ -18133,7 +18077,7 @@
     <row r="11" spans="1:22">
       <c r="B11" s="38"/>
       <c r="C11" s="38"/>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="38"/>
@@ -18173,7 +18117,7 @@
     <row r="12" spans="1:22">
       <c r="B12" s="38"/>
       <c r="C12" s="38"/>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="38"/>
@@ -18213,7 +18157,7 @@
     <row r="13" spans="1:22">
       <c r="B13" s="38"/>
       <c r="C13" s="38"/>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="41" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="38"/>
@@ -18250,7 +18194,7 @@
     <row r="14" spans="1:22">
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
-      <c r="D14" s="42"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="38"/>
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
@@ -18434,7 +18378,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="2:13" ht="15.75" thickBot="1">
+    <row r="28" spans="2:13" ht="15" thickBot="1">
       <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
@@ -18523,7 +18467,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="2:13" ht="15.75" thickBot="1">
+    <row r="34" spans="2:13" ht="15" thickBot="1">
       <c r="B34" s="8" t="s">
         <v>12</v>
       </c>
@@ -18655,7 +18599,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="2:13" ht="15.75" thickBot="1">
+    <row r="42" spans="2:13" ht="15" thickBot="1">
       <c r="B42" s="8" t="s">
         <v>12</v>
       </c>
@@ -18705,46 +18649,46 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15.75" thickBot="1">
+    <row r="54" spans="2:11" ht="15" thickBot="1">
       <c r="B54" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C54" s="52" t="s">
+      <c r="C54" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="52" t="s">
+      <c r="D54" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="51">
         <v>2020</v>
       </c>
-      <c r="F54" s="52">
+      <c r="F54" s="51">
         <v>2025</v>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="51">
         <v>2030</v>
       </c>
-      <c r="H54" s="52">
+      <c r="H54" s="51">
         <v>2035</v>
       </c>
-      <c r="I54" s="52">
+      <c r="I54" s="51">
         <v>2040</v>
       </c>
-      <c r="J54" s="52">
+      <c r="J54" s="51">
         <v>2045</v>
       </c>
-      <c r="K54" s="52">
+      <c r="K54" s="51">
         <v>2050</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="45" t="s">
+      <c r="B55" s="44" t="s">
         <v>183</v>
       </c>
       <c r="C55" s="19">
         <v>34.700000000000003</v>
       </c>
-      <c r="D55" s="48">
+      <c r="D55" s="47">
         <v>9.6388888888888893</v>
       </c>
       <c r="E55" s="19">
@@ -18770,13 +18714,13 @@
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="43" t="s">
+      <c r="B56" s="42" t="s">
         <v>184</v>
       </c>
       <c r="C56" s="19">
         <v>34.700000000000003</v>
       </c>
-      <c r="D56" s="48">
+      <c r="D56" s="47">
         <v>9.6388888888888893</v>
       </c>
       <c r="E56" s="19">
@@ -18802,13 +18746,13 @@
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="43" t="s">
+      <c r="B57" s="42" t="s">
         <v>185</v>
       </c>
       <c r="C57" s="19">
         <v>36.6</v>
       </c>
-      <c r="D57" s="48">
+      <c r="D57" s="47">
         <v>10.166666666666666</v>
       </c>
       <c r="E57" s="19">
@@ -18834,69 +18778,69 @@
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="44">
+      <c r="C58" s="43">
         <v>40.299999999999997</v>
       </c>
-      <c r="D58" s="49">
+      <c r="D58" s="48">
         <v>11.194444444444443</v>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="43">
         <v>0</v>
       </c>
-      <c r="F58" s="44">
+      <c r="F58" s="43">
         <v>0</v>
       </c>
-      <c r="G58" s="44">
+      <c r="G58" s="43">
         <v>0</v>
       </c>
-      <c r="H58" s="44">
+      <c r="H58" s="43">
         <v>3.6</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="43">
         <v>36</v>
       </c>
-      <c r="J58" s="44">
+      <c r="J58" s="43">
         <v>36</v>
       </c>
-      <c r="K58" s="44">
+      <c r="K58" s="43">
         <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:11">
-      <c r="C59" s="47"/>
-      <c r="D59" s="47" t="s">
+      <c r="C59" s="46"/>
+      <c r="D59" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E59" s="46">
         <v>1.8</v>
       </c>
-      <c r="F59" s="47">
+      <c r="F59" s="46">
         <v>5.4</v>
       </c>
-      <c r="G59" s="47">
+      <c r="G59" s="46">
         <v>73.8</v>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="46">
         <v>95.399999999999991</v>
       </c>
-      <c r="I59" s="47">
+      <c r="I59" s="46">
         <v>147.6</v>
       </c>
-      <c r="J59" s="47">
+      <c r="J59" s="46">
         <v>158.4</v>
       </c>
-      <c r="K59" s="47">
+      <c r="K59" s="46">
         <v>158.4</v>
       </c>
     </row>
     <row r="60" spans="2:11">
-      <c r="B60" s="50" t="s">
+      <c r="B60" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C60" s="50" t="s">
         <v>189</v>
       </c>
     </row>
@@ -18909,10 +18853,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F532AC2E-E047-4124-A56C-AD8CA9B97A1E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9">
@@ -18922,7 +18866,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="2:9" ht="15.75" thickBot="1">
+    <row r="4" spans="2:9" ht="15" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -19127,19 +19071,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FB1178-AF9A-473D-9FB3-41C2F896D89C}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B3:M91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="6" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" customWidth="1"/>
+    <col min="11" max="11" width="28.453125" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13">
@@ -19149,7 +19093,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:13" ht="15.75" thickBot="1">
+    <row r="4" spans="2:13" ht="15" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
@@ -19187,10 +19131,10 @@
       <c r="D5" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="I5" s="86" t="str">
+      <c r="I5" s="85" t="str">
         <f>H5</f>
         <v>*0.85</v>
       </c>
@@ -19199,20 +19143,20 @@
       </c>
     </row>
     <row r="6" spans="2:13">
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-    </row>
-    <row r="9" spans="2:13" s="53" customFormat="1"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+    </row>
+    <row r="9" spans="2:13" s="52" customFormat="1"/>
     <row r="11" spans="2:13">
-      <c r="B11" s="74" t="str">
+      <c r="B11" s="73" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C11" s="74"/>
+      <c r="C11" s="73"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="4" t="s">
@@ -19225,34 +19169,34 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="G14" s="76" t="s">
         <v>9</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I14" s="78" t="s">
+      <c r="I14" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="J14" s="78" t="s">
+      <c r="J14" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="K14" s="76" t="s">
+      <c r="K14" s="75" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -19284,11 +19228,11 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="74">
         <f>MIN(C62:H62)/1000</f>
         <v>84.308999999999997</v>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="74">
         <v>5</v>
       </c>
       <c r="K15" s="19" t="s">
@@ -19318,11 +19262,11 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16" s="75">
+      <c r="I16" s="74">
         <f>I15*1.1</f>
         <v>92.739900000000006</v>
       </c>
-      <c r="J16" s="75"/>
+      <c r="J16" s="74"/>
       <c r="K16" s="19"/>
     </row>
     <row r="17" spans="2:13">
@@ -19342,10 +19286,10 @@
       <c r="H17">
         <v>1</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="74">
         <v>0</v>
       </c>
-      <c r="J17" s="75"/>
+      <c r="J17" s="74"/>
       <c r="K17" s="19"/>
     </row>
     <row r="18" spans="2:13">
@@ -19370,11 +19314,11 @@
       <c r="H18">
         <v>1</v>
       </c>
-      <c r="I18" s="75">
+      <c r="I18" s="74">
         <f>1.2*MAX(C74:H74)/1000</f>
         <v>266.64</v>
       </c>
-      <c r="J18" s="75">
+      <c r="J18" s="74">
         <v>5</v>
       </c>
       <c r="K18" s="19" t="s">
@@ -19404,37 +19348,37 @@
       <c r="H19">
         <v>1</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="74">
         <f>+I18*1.3</f>
         <v>346.63200000000001</v>
       </c>
-      <c r="J19" s="75"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="19"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="44"/>
+      <c r="B20" s="43"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="81" t="s">
+      <c r="D20" s="80" t="s">
         <v>196</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="43">
         <v>2050</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H20" s="18">
         <v>1</v>
       </c>
-      <c r="I20" s="79">
+      <c r="I20" s="78">
         <f>I18*5</f>
         <v>1333.1999999999998</v>
       </c>
-      <c r="J20" s="79"/>
-      <c r="K20" s="44"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="43"/>
       <c r="M20" s="18"/>
     </row>
     <row r="21" spans="2:13">
@@ -19449,11 +19393,11 @@
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="74" t="str">
+      <c r="B23" s="73" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C23" s="74"/>
+      <c r="C23" s="73"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="4" t="s">
@@ -19466,34 +19410,34 @@
       </c>
     </row>
     <row r="26" spans="2:13">
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="77" t="s">
+      <c r="C26" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="77" t="s">
+      <c r="E26" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="F26" s="77" t="s">
+      <c r="F26" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="77" t="s">
+      <c r="G26" s="76" t="s">
         <v>9</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I26" s="78" t="s">
+      <c r="I26" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="J26" s="78" t="s">
+      <c r="J26" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="K26" s="76" t="s">
+      <c r="K26" s="75" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="5" t="s">
@@ -19525,7 +19469,7 @@
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27" s="82">
+      <c r="I27" s="81">
         <f>MIN(C78:H78)*0.5/1000</f>
         <v>1.0561541074426846</v>
       </c>
@@ -19559,7 +19503,7 @@
       <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="82">
+      <c r="I28" s="81">
         <v>0</v>
       </c>
       <c r="K28" s="19"/>
@@ -19581,7 +19525,7 @@
       <c r="H29">
         <v>1</v>
       </c>
-      <c r="I29" s="82">
+      <c r="I29" s="81">
         <v>0</v>
       </c>
       <c r="K29" s="19"/>
@@ -19608,7 +19552,7 @@
       <c r="H30">
         <v>1</v>
       </c>
-      <c r="I30" s="82">
+      <c r="I30" s="81">
         <f>2*MAX(C78:H78)/1000</f>
         <v>5.370076461803917</v>
       </c>
@@ -19626,47 +19570,47 @@
       </c>
     </row>
     <row r="31" spans="2:13">
-      <c r="B31" s="44"/>
+      <c r="B31" s="43"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="81" t="s">
+      <c r="D31" s="80" t="s">
         <v>201</v>
       </c>
       <c r="E31" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="43">
         <v>2040</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H31" s="18">
         <v>1</v>
       </c>
-      <c r="I31" s="80">
+      <c r="I31" s="79">
         <f>I30*2</f>
         <v>10.740152923607834</v>
       </c>
       <c r="J31" s="18"/>
-      <c r="K31" s="44"/>
+      <c r="K31" s="43"/>
     </row>
     <row r="32" spans="2:13">
-      <c r="D32" s="81" t="s">
+      <c r="D32" s="80" t="s">
         <v>201</v>
       </c>
       <c r="E32" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="43">
         <v>2050</v>
       </c>
-      <c r="G32" s="44" t="s">
+      <c r="G32" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H32" s="18">
         <v>1</v>
       </c>
-      <c r="I32" s="80">
+      <c r="I32" s="79">
         <f>I31*5</f>
         <v>53.700764618039173</v>
       </c>
@@ -19681,11 +19625,11 @@
       <c r="G34" s="19"/>
     </row>
     <row r="35" spans="2:13">
-      <c r="B35" s="74" t="str">
+      <c r="B35" s="73" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C35" s="74"/>
+      <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="4" t="s">
@@ -19698,34 +19642,34 @@
       </c>
     </row>
     <row r="38" spans="2:13">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C38" s="77" t="s">
+      <c r="C38" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="D38" s="77" t="s">
+      <c r="D38" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="77" t="s">
+      <c r="E38" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="F38" s="77" t="s">
+      <c r="F38" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="77" t="s">
+      <c r="G38" s="76" t="s">
         <v>9</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I38" s="78" t="s">
+      <c r="I38" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="J38" s="78" t="s">
+      <c r="J38" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="K38" s="76" t="s">
+      <c r="K38" s="75" t="s">
         <v>11</v>
       </c>
       <c r="L38" s="5" t="s">
@@ -19757,7 +19701,7 @@
       <c r="H39">
         <v>1</v>
       </c>
-      <c r="I39" s="82">
+      <c r="I39" s="81">
         <f>MIN(C77:H77)*0.5/1000</f>
         <v>0.45905338863054296</v>
       </c>
@@ -19791,7 +19735,7 @@
       <c r="H40">
         <v>1</v>
       </c>
-      <c r="I40" s="82">
+      <c r="I40" s="81">
         <v>0</v>
       </c>
       <c r="J40" s="19"/>
@@ -19814,7 +19758,7 @@
       <c r="H41">
         <v>1</v>
       </c>
-      <c r="I41" s="82">
+      <c r="I41" s="81">
         <v>0</v>
       </c>
       <c r="J41" s="19"/>
@@ -19842,7 +19786,7 @@
       <c r="H42">
         <v>1</v>
       </c>
-      <c r="I42" s="82">
+      <c r="I42" s="81">
         <f>2*MAX(C77:H77)/1000</f>
         <v>2.3340834255383354</v>
       </c>
@@ -19860,47 +19804,47 @@
       </c>
     </row>
     <row r="43" spans="2:13">
-      <c r="B43" s="44"/>
+      <c r="B43" s="43"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="81" t="s">
+      <c r="D43" s="80" t="s">
         <v>200</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F43" s="44">
+      <c r="F43" s="43">
         <v>2040</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H43" s="18">
         <v>1</v>
       </c>
-      <c r="I43" s="80">
+      <c r="I43" s="79">
         <f>I42*2</f>
         <v>4.6681668510766707</v>
       </c>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
     </row>
     <row r="44" spans="2:13">
-      <c r="D44" s="81" t="s">
+      <c r="D44" s="80" t="s">
         <v>200</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F44" s="44">
+      <c r="F44" s="43">
         <v>2050</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H44" s="18">
         <v>1</v>
       </c>
-      <c r="I44" s="80">
+      <c r="I44" s="79">
         <f>I43*5</f>
         <v>23.340834255383353</v>
       </c>
@@ -19909,62 +19853,62 @@
     <row r="45" spans="2:13">
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="I45" s="83"/>
+      <c r="I45" s="82"/>
     </row>
     <row r="46" spans="2:13">
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="I46" s="83"/>
+      <c r="I46" s="82"/>
     </row>
     <row r="47" spans="2:13">
-      <c r="B47" s="74" t="str">
+      <c r="B47" s="73" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C47" s="74"/>
-      <c r="I47" s="83"/>
+      <c r="C47" s="73"/>
+      <c r="I47" s="82"/>
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I48" s="83"/>
+      <c r="I48" s="82"/>
     </row>
     <row r="49" spans="2:13">
       <c r="G49" t="s">
         <v>7</v>
       </c>
-      <c r="I49" s="83"/>
+      <c r="I49" s="82"/>
     </row>
     <row r="50" spans="2:13">
-      <c r="B50" s="76" t="s">
+      <c r="B50" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="77" t="s">
+      <c r="C50" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="D50" s="77" t="s">
+      <c r="D50" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="77" t="s">
+      <c r="E50" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="F50" s="77" t="s">
+      <c r="F50" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="G50" s="77" t="s">
+      <c r="G50" s="76" t="s">
         <v>9</v>
       </c>
       <c r="H50" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I50" s="78" t="s">
+      <c r="I50" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="J50" s="78" t="s">
+      <c r="J50" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="K50" s="76" t="s">
+      <c r="K50" s="75" t="s">
         <v>11</v>
       </c>
       <c r="L50" s="5" t="s">
@@ -19996,7 +19940,7 @@
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" s="82">
+      <c r="I51" s="81">
         <f>MIN(C76:H76)*0.5/1000</f>
         <v>14.343833406839419</v>
       </c>
@@ -20030,7 +19974,7 @@
       <c r="H52">
         <v>1</v>
       </c>
-      <c r="I52" s="82">
+      <c r="I52" s="81">
         <v>0</v>
       </c>
       <c r="J52" s="19"/>
@@ -20055,7 +19999,7 @@
       <c r="H53">
         <v>1</v>
       </c>
-      <c r="I53" s="82">
+      <c r="I53" s="81">
         <v>0</v>
       </c>
       <c r="J53" s="19"/>
@@ -20083,7 +20027,7 @@
       <c r="H54">
         <v>1</v>
       </c>
-      <c r="I54" s="82">
+      <c r="I54" s="81">
         <f>2*MAX(C76:H76)/1000</f>
         <v>72.932048085875735</v>
       </c>
@@ -20101,49 +20045,49 @@
       </c>
     </row>
     <row r="55" spans="2:13">
-      <c r="B55" s="44"/>
+      <c r="B55" s="43"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="81" t="s">
+      <c r="D55" s="80" t="s">
         <v>199</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="44">
+      <c r="F55" s="43">
         <v>2040</v>
       </c>
-      <c r="G55" s="44" t="s">
+      <c r="G55" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H55" s="18">
         <v>1</v>
       </c>
-      <c r="I55" s="80">
+      <c r="I55" s="79">
         <f>I54*2</f>
         <v>145.86409617175147</v>
       </c>
-      <c r="J55" s="44"/>
-      <c r="K55" s="44" t="s">
+      <c r="J55" s="43"/>
+      <c r="K55" s="43" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="56" spans="2:13">
-      <c r="D56" s="81" t="s">
+      <c r="D56" s="80" t="s">
         <v>199</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="44">
+      <c r="F56" s="43">
         <v>2050</v>
       </c>
-      <c r="G56" s="44" t="s">
+      <c r="G56" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H56" s="18">
         <v>1</v>
       </c>
-      <c r="I56" s="80">
+      <c r="I56" s="79">
         <f>I55*5</f>
         <v>729.32048085875738</v>
       </c>
@@ -20154,247 +20098,247 @@
       <c r="G57" s="19"/>
     </row>
     <row r="60" spans="2:13">
-      <c r="B60" s="58" t="s">
+      <c r="B60" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-    </row>
-    <row r="61" spans="2:13" ht="15.75">
-      <c r="B61" s="58"/>
-      <c r="C61" s="64">
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+    </row>
+    <row r="61" spans="2:13" ht="15.5">
+      <c r="B61" s="57"/>
+      <c r="C61" s="63">
         <v>2018</v>
       </c>
-      <c r="D61" s="64">
+      <c r="D61" s="63">
         <v>2019</v>
       </c>
-      <c r="E61" s="64">
+      <c r="E61" s="63">
         <v>2020</v>
       </c>
-      <c r="F61" s="64">
+      <c r="F61" s="63">
         <v>2021</v>
       </c>
-      <c r="G61" s="64">
+      <c r="G61" s="63">
         <v>2022</v>
       </c>
-      <c r="H61" s="64">
+      <c r="H61" s="63">
         <v>2023</v>
       </c>
     </row>
     <row r="62" spans="2:13">
-      <c r="B62" s="59" t="s">
+      <c r="B62" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="C62" s="60">
+      <c r="C62" s="59">
         <v>121157</v>
       </c>
-      <c r="D62" s="60">
+      <c r="D62" s="59">
         <v>113305</v>
       </c>
-      <c r="E62" s="60">
+      <c r="E62" s="59">
         <v>84309</v>
       </c>
-      <c r="F62" s="60">
+      <c r="F62" s="59">
         <v>101853</v>
       </c>
-      <c r="G62" s="60">
+      <c r="G62" s="59">
         <v>101349</v>
       </c>
-      <c r="H62" s="60">
+      <c r="H62" s="59">
         <v>117424</v>
       </c>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="59" t="s">
+      <c r="B63" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="60">
+      <c r="C63" s="59">
         <v>25459</v>
       </c>
-      <c r="D63" s="60">
+      <c r="D63" s="59">
         <v>24645</v>
       </c>
-      <c r="E63" s="60">
+      <c r="E63" s="59">
         <v>21495</v>
       </c>
-      <c r="F63" s="60">
+      <c r="F63" s="59">
         <v>28387</v>
       </c>
-      <c r="G63" s="60">
+      <c r="G63" s="59">
         <v>23655</v>
       </c>
-      <c r="H63" s="60">
+      <c r="H63" s="59">
         <v>29038</v>
       </c>
     </row>
     <row r="64" spans="2:13">
-      <c r="B64" s="59" t="s">
+      <c r="B64" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="C64" s="60">
+      <c r="C64" s="59">
         <v>157865</v>
       </c>
-      <c r="D64" s="60">
+      <c r="D64" s="59">
         <v>149748</v>
       </c>
-      <c r="E64" s="60">
+      <c r="E64" s="59">
         <v>10710</v>
       </c>
-      <c r="F64" s="60">
+      <c r="F64" s="59">
         <v>12136</v>
       </c>
-      <c r="G64" s="60">
+      <c r="G64" s="59">
         <v>12244</v>
       </c>
-      <c r="H64" s="60">
+      <c r="H64" s="59">
         <v>13316</v>
       </c>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="59" t="s">
+      <c r="B65" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="C65" s="63">
+      <c r="C65" s="62">
         <v>304481</v>
       </c>
-      <c r="D65" s="63">
+      <c r="D65" s="62">
         <v>287698</v>
       </c>
-      <c r="E65" s="63">
+      <c r="E65" s="62">
         <v>116514</v>
       </c>
-      <c r="F65" s="63">
+      <c r="F65" s="62">
         <v>142376</v>
       </c>
-      <c r="G65" s="63">
+      <c r="G65" s="62">
         <v>137248</v>
       </c>
-      <c r="H65" s="63">
+      <c r="H65" s="62">
         <v>159778</v>
       </c>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <v>99456</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="59">
         <v>108895</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="59">
         <v>78541</v>
       </c>
-      <c r="F66" s="60">
+      <c r="F66" s="59">
         <v>68042</v>
       </c>
-      <c r="G66" s="60">
+      <c r="G66" s="59">
         <v>46567</v>
       </c>
-      <c r="H66" s="60">
+      <c r="H66" s="59">
         <v>50381</v>
       </c>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="59" t="s">
+      <c r="B67" s="58" t="s">
         <v>208</v>
       </c>
-      <c r="C67" s="60">
+      <c r="C67" s="59">
         <v>14859</v>
       </c>
-      <c r="D67" s="60">
+      <c r="D67" s="59">
         <v>15152</v>
       </c>
-      <c r="E67" s="60">
+      <c r="E67" s="59">
         <v>11573</v>
       </c>
-      <c r="F67" s="60">
+      <c r="F67" s="59">
         <v>10631</v>
       </c>
-      <c r="G67" s="60">
+      <c r="G67" s="59">
         <v>8063</v>
       </c>
-      <c r="H67" s="60">
+      <c r="H67" s="59">
         <v>9443</v>
       </c>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="59" t="s">
+      <c r="B68" s="58" t="s">
         <v>209</v>
       </c>
-      <c r="C68" s="60">
+      <c r="C68" s="59">
         <v>125874</v>
       </c>
-      <c r="D68" s="60">
+      <c r="D68" s="59">
         <v>137196</v>
       </c>
-      <c r="E68" s="60">
+      <c r="E68" s="59">
         <v>11178</v>
       </c>
-      <c r="F68" s="60">
+      <c r="F68" s="59">
         <v>13288</v>
       </c>
-      <c r="G68" s="60">
+      <c r="G68" s="59">
         <v>10823</v>
       </c>
-      <c r="H68" s="60">
+      <c r="H68" s="59">
         <v>11011</v>
       </c>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="61" t="s">
+      <c r="B69" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="62">
+      <c r="C69" s="61">
         <v>240189</v>
       </c>
-      <c r="D69" s="62">
+      <c r="D69" s="61">
         <v>261243</v>
       </c>
-      <c r="E69" s="62">
+      <c r="E69" s="61">
         <v>101472</v>
       </c>
-      <c r="F69" s="62">
+      <c r="F69" s="61">
         <v>91961</v>
       </c>
-      <c r="G69" s="62">
+      <c r="G69" s="61">
         <v>65453</v>
       </c>
-      <c r="H69" s="62">
+      <c r="H69" s="61">
         <v>70835</v>
       </c>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="59" t="s">
+      <c r="B70" s="58" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="64" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="15.75">
-      <c r="B73" s="59" t="s">
+    <row r="73" spans="2:8" ht="15.5">
+      <c r="B73" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="C73" s="64">
+      <c r="C73" s="63">
         <v>2018</v>
       </c>
-      <c r="D73" s="64">
+      <c r="D73" s="63">
         <v>2019</v>
       </c>
-      <c r="E73" s="64">
+      <c r="E73" s="63">
         <v>2020</v>
       </c>
-      <c r="F73" s="64">
+      <c r="F73" s="63">
         <v>2021</v>
       </c>
-      <c r="G73" s="64">
+      <c r="G73" s="63">
         <v>2022</v>
       </c>
-      <c r="H73" s="64">
+      <c r="H73" s="63">
         <v>2023</v>
       </c>
     </row>
@@ -20402,27 +20346,27 @@
       <c r="B74" t="s">
         <v>214</v>
       </c>
-      <c r="C74" s="56">
+      <c r="C74" s="55">
         <f>C62+C66</f>
         <v>220613</v>
       </c>
-      <c r="D74" s="56">
+      <c r="D74" s="55">
         <f t="shared" ref="D74:H74" si="0">D62+D66</f>
         <v>222200</v>
       </c>
-      <c r="E74" s="56">
+      <c r="E74" s="55">
         <f t="shared" si="0"/>
         <v>162850</v>
       </c>
-      <c r="F74" s="56">
+      <c r="F74" s="55">
         <f t="shared" si="0"/>
         <v>169895</v>
       </c>
-      <c r="G74" s="56">
+      <c r="G74" s="55">
         <f t="shared" si="0"/>
         <v>147916</v>
       </c>
-      <c r="H74" s="56">
+      <c r="H74" s="55">
         <f t="shared" si="0"/>
         <v>167805</v>
       </c>
@@ -20431,27 +20375,27 @@
       <c r="B75" t="s">
         <v>215</v>
       </c>
-      <c r="C75" s="56">
+      <c r="C75" s="55">
         <f>C63+C67</f>
         <v>40318</v>
       </c>
-      <c r="D75" s="56">
+      <c r="D75" s="55">
         <f t="shared" ref="D75:H75" si="1">D63+D67</f>
         <v>39797</v>
       </c>
-      <c r="E75" s="56">
+      <c r="E75" s="55">
         <f t="shared" si="1"/>
         <v>33068</v>
       </c>
-      <c r="F75" s="56">
+      <c r="F75" s="55">
         <f t="shared" si="1"/>
         <v>39018</v>
       </c>
-      <c r="G75" s="56">
+      <c r="G75" s="55">
         <f t="shared" si="1"/>
         <v>31718</v>
       </c>
-      <c r="H75" s="56">
+      <c r="H75" s="55">
         <f t="shared" si="1"/>
         <v>38481</v>
       </c>
@@ -20460,27 +20404,27 @@
       <c r="B76" t="s">
         <v>216</v>
       </c>
-      <c r="C76" s="56">
+      <c r="C76" s="55">
         <f>C75*$G$88</f>
         <v>36466.024042937868</v>
       </c>
-      <c r="D76" s="56">
+      <c r="D76" s="55">
         <f t="shared" ref="D76:H76" si="2">D75*$G$88</f>
         <v>35994.800308467646</v>
       </c>
-      <c r="E76" s="56">
+      <c r="E76" s="55">
         <f t="shared" si="2"/>
         <v>29908.688006643919</v>
       </c>
-      <c r="F76" s="56">
+      <c r="F76" s="55">
         <f t="shared" si="2"/>
         <v>35290.225857119643</v>
       </c>
-      <c r="G76" s="56">
+      <c r="G76" s="55">
         <f t="shared" si="2"/>
         <v>28687.666813678839</v>
       </c>
-      <c r="H76" s="56">
+      <c r="H76" s="55">
         <f t="shared" si="2"/>
         <v>34804.530760362424</v>
       </c>
@@ -20489,27 +20433,27 @@
       <c r="B77" t="s">
         <v>217</v>
       </c>
-      <c r="C77" s="56">
+      <c r="C77" s="55">
         <f>C75*$G$89</f>
         <v>1167.0417127691676</v>
       </c>
-      <c r="D77" s="56">
+      <c r="D77" s="55">
         <f t="shared" ref="D77:H77" si="3">D75*$G$89</f>
         <v>1151.9608870250152</v>
       </c>
-      <c r="E77" s="56">
+      <c r="E77" s="55">
         <f t="shared" si="3"/>
         <v>957.18377295130801</v>
       </c>
-      <c r="F77" s="56">
+      <c r="F77" s="55">
         <f t="shared" si="3"/>
         <v>1129.4120132156204</v>
       </c>
-      <c r="G77" s="56">
+      <c r="G77" s="55">
         <f t="shared" si="3"/>
         <v>918.10677726108588</v>
       </c>
-      <c r="H77" s="56">
+      <c r="H77" s="55">
         <f t="shared" si="3"/>
         <v>1113.868052707732</v>
       </c>
@@ -20518,27 +20462,27 @@
       <c r="B78" t="s">
         <v>218</v>
       </c>
-      <c r="C78" s="56">
+      <c r="C78" s="55">
         <f>C75*$G$90</f>
         <v>2685.0382309019583</v>
       </c>
-      <c r="D78" s="56">
+      <c r="D78" s="55">
         <f t="shared" ref="D78:H78" si="4">D75*$G$90</f>
         <v>2650.3414473735111</v>
       </c>
-      <c r="E78" s="56">
+      <c r="E78" s="55">
         <f t="shared" si="4"/>
         <v>2202.2135080972753</v>
       </c>
-      <c r="F78" s="56">
+      <c r="F78" s="55">
         <f t="shared" si="4"/>
         <v>2598.4627633645669</v>
       </c>
-      <c r="G78" s="56">
+      <c r="G78" s="55">
         <f t="shared" si="4"/>
         <v>2112.3082148853691</v>
       </c>
-      <c r="H78" s="56">
+      <c r="H78" s="55">
         <f t="shared" si="4"/>
         <v>2562.7004356202751</v>
       </c>
@@ -20549,10 +20493,10 @@
       </c>
     </row>
     <row r="83" spans="2:8">
-      <c r="B83" s="67" t="s">
+      <c r="B83" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="68" t="s">
+      <c r="C83" s="67" t="s">
         <v>221</v>
       </c>
       <c r="G83">
@@ -20563,10 +20507,10 @@
       </c>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="69" t="s">
+      <c r="B84" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="C84" s="70">
+      <c r="C84" s="69">
         <v>387723</v>
       </c>
       <c r="F84" t="s">
@@ -20576,15 +20520,15 @@
         <f>C85+C86</f>
         <v>350680</v>
       </c>
-      <c r="H84" s="55">
+      <c r="H84" s="54">
         <v>771496.00000000012</v>
       </c>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="71" t="s">
+      <c r="B85" s="70" t="s">
         <v>223</v>
       </c>
-      <c r="C85" s="72">
+      <c r="C85" s="71">
         <v>222953</v>
       </c>
       <c r="F85" t="s">
@@ -20594,15 +20538,15 @@
         <f>C87+C88</f>
         <v>11223</v>
       </c>
-      <c r="H85" s="55">
+      <c r="H85" s="54">
         <v>24690.600000000002</v>
       </c>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="69" t="s">
+      <c r="B86" s="68" t="s">
         <v>224</v>
       </c>
-      <c r="C86" s="70">
+      <c r="C86" s="69">
         <v>127727</v>
       </c>
       <c r="F86" t="s">
@@ -20612,15 +20556,15 @@
         <f>C89+C90</f>
         <v>25821</v>
       </c>
-      <c r="H86" s="55">
+      <c r="H86" s="54">
         <v>56806.200000000004</v>
       </c>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="71" t="s">
+      <c r="B87" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="C87" s="72">
+      <c r="C87" s="71">
         <v>4421</v>
       </c>
       <c r="G87" t="s">
@@ -20628,57 +20572,57 @@
       </c>
     </row>
     <row r="88" spans="2:8">
-      <c r="B88" s="69" t="s">
+      <c r="B88" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="70">
+      <c r="C88" s="69">
         <v>6802</v>
       </c>
       <c r="F88" t="s">
         <v>216</v>
       </c>
-      <c r="G88" s="54">
+      <c r="G88" s="53">
         <f>G84/$C$84</f>
         <v>0.90446014293709687</v>
       </c>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="71" t="s">
+      <c r="B89" s="70" t="s">
         <v>228</v>
       </c>
-      <c r="C89" s="72">
+      <c r="C89" s="71">
         <v>9100</v>
       </c>
       <c r="F89" t="s">
         <v>217</v>
       </c>
-      <c r="G89" s="54">
+      <c r="G89" s="53">
         <f t="shared" ref="G89:G90" si="5">G85/$C$84</f>
         <v>2.8945922733497883E-2</v>
       </c>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="73" t="s">
+      <c r="B90" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="65">
         <v>16721</v>
       </c>
       <c r="F90" t="s">
         <v>218</v>
       </c>
-      <c r="G90" s="54">
+      <c r="G90" s="53">
         <f t="shared" si="5"/>
         <v>6.659651349030106E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
-      <c r="B91" s="57" t="s">
+      <c r="B91" s="56" t="s">
         <v>230</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="49" type="noConversion"/>
+  <phoneticPr fontId="48" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B71" r:id="rId1" location=":~:text=The%20number%20of%20new%20cars,2022%20(50%2C381%20versus%2046%2C567)." xr:uid="{D6FC7503-56E3-4D02-ABAF-AE1C4A4C08B4}"/>
   </hyperlinks>
